--- a/research/traditional_assets/database/data/bahrain/bahrain_hotel_gaming.xlsx
+++ b/research/traditional_assets/database/data/bahrain/bahrain_hotel_gaming.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="bax_ghg" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -351,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +581,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,43 +590,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0984</v>
+        <v>-0.0427</v>
+      </c>
+      <c r="E2">
+        <v>-0.0877</v>
       </c>
       <c r="G2">
-        <v>0.09401869158878505</v>
+        <v>0.1821792260692465</v>
       </c>
       <c r="H2">
-        <v>0.09401869158878505</v>
+        <v>0.1821792260692465</v>
       </c>
       <c r="I2">
-        <v>-0.1452336448598131</v>
+        <v>0.06873727087576376</v>
       </c>
       <c r="J2">
-        <v>-0.1452336448598131</v>
+        <v>0.06873727087576376</v>
       </c>
       <c r="K2">
-        <v>-8.6</v>
+        <v>23.81</v>
       </c>
       <c r="L2">
-        <v>-0.1607476635514019</v>
+        <v>0.2424643584521385</v>
       </c>
       <c r="M2">
-        <v>6.24</v>
+        <v>15.28</v>
       </c>
       <c r="N2">
-        <v>0.03349436392914654</v>
+        <v>0.05720703856233621</v>
       </c>
       <c r="O2">
-        <v>-0.7255813953488373</v>
+        <v>0.6417471650566988</v>
       </c>
       <c r="P2">
-        <v>6.24</v>
+        <v>15.28</v>
       </c>
       <c r="Q2">
-        <v>0.03349436392914654</v>
+        <v>0.05720703856233621</v>
       </c>
       <c r="R2">
-        <v>-0.7255813953488373</v>
+        <v>0.6417471650566988</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -633,73 +638,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>10.8</v>
+        <v>22.35</v>
       </c>
       <c r="V2">
-        <v>0.05797101449275362</v>
+        <v>0.08367652564582555</v>
       </c>
       <c r="W2">
-        <v>-0.03129548762736535</v>
+        <v>0.04783194355715036</v>
       </c>
       <c r="X2">
-        <v>0.113070512327835</v>
+        <v>0.1560977812696164</v>
       </c>
       <c r="Y2">
-        <v>-0.1443659999552004</v>
+        <v>-0.1082658377124661</v>
       </c>
       <c r="Z2">
-        <v>0.1804993252361673</v>
+        <v>0.2111464694246151</v>
       </c>
       <c r="AA2">
-        <v>-0.02621457489878542</v>
+        <v>0.011359620064333</v>
       </c>
       <c r="AB2">
-        <v>0.1101241167107049</v>
+        <v>0.1556001181073737</v>
       </c>
       <c r="AC2">
-        <v>-0.1363386916094903</v>
+        <v>-0.1442404980430407</v>
       </c>
       <c r="AD2">
-        <v>17</v>
+        <v>7.15</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>17</v>
+        <v>7.15</v>
       </c>
       <c r="AG2">
-        <v>6.199999999999999</v>
+        <v>-15.2</v>
       </c>
       <c r="AH2">
-        <v>0.08362026561731431</v>
+        <v>0.0260711030082042</v>
       </c>
       <c r="AI2">
-        <v>0.06099748833871547</v>
+        <v>0.01484480431848853</v>
       </c>
       <c r="AJ2">
-        <v>0.03220779220779221</v>
+        <v>-0.06034140531957127</v>
       </c>
       <c r="AK2">
-        <v>0.02314296379245987</v>
+        <v>-0.03309383844981494</v>
       </c>
       <c r="AL2">
-        <v>1.36</v>
+        <v>0.387</v>
       </c>
       <c r="AM2">
-        <v>0.05000000000000004</v>
+        <v>-1.84</v>
       </c>
       <c r="AN2">
-        <v>1.750772399588053</v>
+        <v>0.2455357142857143</v>
       </c>
       <c r="AO2">
-        <v>-5.713235294117647</v>
+        <v>17.44186046511628</v>
       </c>
       <c r="AP2">
-        <v>0.6385169927909371</v>
+        <v>-0.521978021978022</v>
       </c>
       <c r="AQ2">
-        <v>-155.3999999999999</v>
+        <v>-3.668478260869565</v>
       </c>
     </row>
     <row r="3">
@@ -719,43 +724,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0984</v>
+        <v>-0.0411</v>
+      </c>
+      <c r="E3">
+        <v>-0.08359999999999999</v>
       </c>
       <c r="G3">
-        <v>0.09401869158878505</v>
+        <v>0.1808118081180812</v>
       </c>
       <c r="H3">
-        <v>0.09401869158878505</v>
+        <v>0.1808118081180812</v>
       </c>
       <c r="I3">
-        <v>-0.1452336448598131</v>
+        <v>0.1057810578105781</v>
       </c>
       <c r="J3">
-        <v>-0.1452336448598131</v>
+        <v>0.1057810578105781</v>
       </c>
       <c r="K3">
-        <v>-8.6</v>
+        <v>19.4</v>
       </c>
       <c r="L3">
-        <v>-0.1607476635514019</v>
+        <v>0.2386223862238622</v>
       </c>
       <c r="M3">
-        <v>6.24</v>
+        <v>12.1</v>
       </c>
       <c r="N3">
-        <v>0.03349436392914654</v>
+        <v>0.05457825890843482</v>
       </c>
       <c r="O3">
-        <v>-0.7255813953488373</v>
+        <v>0.6237113402061856</v>
       </c>
       <c r="P3">
-        <v>6.24</v>
+        <v>12.1</v>
       </c>
       <c r="Q3">
-        <v>0.03349436392914654</v>
+        <v>0.05457825890843482</v>
       </c>
       <c r="R3">
-        <v>-0.7255813953488373</v>
+        <v>0.6237113402061856</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,73 +772,8916 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>10.8</v>
+        <v>19.1</v>
       </c>
       <c r="V3">
-        <v>0.05797101449275362</v>
+        <v>0.08615245827695084</v>
       </c>
       <c r="W3">
-        <v>-0.03129548762736535</v>
+        <v>0.07413068398930073</v>
       </c>
       <c r="X3">
-        <v>0.113070512327835</v>
+        <v>0.1579592375698667</v>
       </c>
       <c r="Y3">
-        <v>-0.1443659999552004</v>
+        <v>-0.08382855358056598</v>
       </c>
       <c r="Z3">
-        <v>0.1804993252361673</v>
+        <v>0.303471444568869</v>
       </c>
       <c r="AA3">
-        <v>-0.02621457489878542</v>
+        <v>0.03210153042179918</v>
       </c>
       <c r="AB3">
-        <v>0.1101241167107049</v>
+        <v>0.1569639112453813</v>
       </c>
       <c r="AC3">
-        <v>-0.1363386916094903</v>
+        <v>-0.1248623808235821</v>
       </c>
       <c r="AD3">
-        <v>17</v>
+        <v>7.15</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>17</v>
+        <v>7.15</v>
       </c>
       <c r="AG3">
-        <v>6.199999999999999</v>
+        <v>-11.95</v>
       </c>
       <c r="AH3">
-        <v>0.08362026561731431</v>
+        <v>0.03124317238365742</v>
       </c>
       <c r="AI3">
-        <v>0.06099748833871547</v>
+        <v>0.02593869036822057</v>
       </c>
       <c r="AJ3">
-        <v>0.03220779220779221</v>
+        <v>-0.05697258641239571</v>
       </c>
       <c r="AK3">
-        <v>0.02314296379245987</v>
+        <v>-0.04657961411030988</v>
       </c>
       <c r="AL3">
-        <v>1.36</v>
+        <v>0.387</v>
       </c>
       <c r="AM3">
-        <v>0.05000000000000004</v>
+        <v>-0.883</v>
       </c>
       <c r="AN3">
-        <v>1.750772399588053</v>
+        <v>0.2954545454545455</v>
       </c>
       <c r="AO3">
-        <v>-5.713235294117647</v>
+        <v>22.22222222222222</v>
       </c>
       <c r="AP3">
-        <v>0.6385169927909371</v>
+        <v>-0.4938016528925621</v>
       </c>
       <c r="AQ3">
-        <v>-155.3999999999999</v>
+        <v>-9.739524348810871</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Bahrain</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>National Hotels Company B.S.C. (BAX:NHOTEL)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Hotel/Gaming</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>-0.0443</v>
+      </c>
+      <c r="E4">
+        <v>-0.09179999999999999</v>
+      </c>
+      <c r="G4">
+        <v>0.1887573964497042</v>
+      </c>
+      <c r="H4">
+        <v>0.1887573964497042</v>
+      </c>
+      <c r="I4">
+        <v>-0.1094674556213018</v>
+      </c>
+      <c r="J4">
+        <v>-0.1094674556213018</v>
+      </c>
+      <c r="K4">
+        <v>4.41</v>
+      </c>
+      <c r="L4">
+        <v>0.2609467455621302</v>
+      </c>
+      <c r="M4">
+        <v>3.18</v>
+      </c>
+      <c r="N4">
+        <v>0.07004405286343612</v>
+      </c>
+      <c r="O4">
+        <v>0.7210884353741497</v>
+      </c>
+      <c r="P4">
+        <v>3.18</v>
+      </c>
+      <c r="Q4">
+        <v>0.07004405286343612</v>
+      </c>
+      <c r="R4">
+        <v>0.7210884353741497</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>3.25</v>
+      </c>
+      <c r="V4">
+        <v>0.07158590308370044</v>
+      </c>
+      <c r="W4">
+        <v>0.021533203125</v>
+      </c>
+      <c r="X4">
+        <v>0.1542363249693662</v>
+      </c>
+      <c r="Y4">
+        <v>-0.1327031218443662</v>
+      </c>
+      <c r="Z4">
+        <v>0.08570848970483821</v>
+      </c>
+      <c r="AA4">
+        <v>-0.009382290293133177</v>
+      </c>
+      <c r="AB4">
+        <v>0.1542363249693662</v>
+      </c>
+      <c r="AC4">
+        <v>-0.1636186152624994</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>-3.25</v>
+      </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <v>-0.0771055753262159</v>
+      </c>
+      <c r="AK4">
+        <v>-0.01602959309494451</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>-0.957</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>-0.6605691056910569</v>
+      </c>
+      <c r="AQ4">
+        <v>1.933124346917451</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Gulf Hotels Group B.S.C. (BAX:GHG)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BAX:GHG</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Hotel/Gaming</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Bahrain</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.0312431723836574</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>221.7</v>
+      </c>
+      <c r="H2">
+        <v>233.806076187855</v>
+      </c>
+      <c r="I2">
+        <v>209.75</v>
+      </c>
+      <c r="J2">
+        <v>214.706076187855</v>
+      </c>
+      <c r="K2">
+        <v>7.15</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0.156963911245381</v>
+      </c>
+      <c r="N2">
+        <v>0.154236324969366</v>
+      </c>
+      <c r="O2">
+        <v>0.126101834862385</v>
+      </c>
+      <c r="P2">
+        <v>0.0457</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.157959237569867</v>
+      </c>
+      <c r="T2">
+        <v>0.154236324969366</v>
+      </c>
+      <c r="U2">
+        <v>0.7733594025056399</v>
+      </c>
+      <c r="V2">
+        <v>0.749197201378634</v>
+      </c>
+      <c r="W2">
+        <v>10000000</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>221.7</v>
+      </c>
+      <c r="AB2">
+        <v>0.1540800269367614</v>
+      </c>
+      <c r="AC2">
+        <v>0.1261018348623854</v>
+      </c>
+      <c r="AD2">
+        <v>0</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>24.2</v>
+      </c>
+      <c r="AH2">
+        <v>15.5</v>
+      </c>
+      <c r="AI2">
+        <v>0.8590000000000018</v>
+      </c>
+      <c r="AJ2">
+        <v>7.15</v>
+      </c>
+      <c r="AK2">
+        <v>7.15</v>
+      </c>
+      <c r="AL2">
+        <v>0.387</v>
+      </c>
+      <c r="AM2">
+        <v>7.15</v>
+      </c>
+      <c r="AN2">
+        <v>19.1</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1542363249693662</v>
+      </c>
+      <c r="C2">
+        <v>233.806076187855</v>
+      </c>
+      <c r="D2">
+        <v>214.706076187855</v>
+      </c>
+      <c r="E2">
+        <v>-7.15</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>19.1</v>
+      </c>
+      <c r="H2">
+        <v>221.7</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>24.2</v>
+      </c>
+      <c r="K2">
+        <v>15.5</v>
+      </c>
+      <c r="L2">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="Q2">
+        <v>24.2</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1542363249693662</v>
+      </c>
+      <c r="T2">
+        <v>0.7491972013786339</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <v>0.0457</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1543053249693662</v>
+      </c>
+      <c r="C3">
+        <v>231.3893161335164</v>
+      </c>
+      <c r="D3">
+        <v>214.5778161335164</v>
+      </c>
+      <c r="E3">
+        <v>-4.8615</v>
+      </c>
+      <c r="F3">
+        <v>2.2885</v>
+      </c>
+      <c r="G3">
+        <v>19.1</v>
+      </c>
+      <c r="H3">
+        <v>221.7</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>24.2</v>
+      </c>
+      <c r="K3">
+        <v>15.5</v>
+      </c>
+      <c r="L3">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M3">
+        <v>0.10458445</v>
+      </c>
+      <c r="N3">
+        <v>8.595415549999998</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>8.595415549999998</v>
+      </c>
+      <c r="Q3">
+        <v>24.09541555</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1554023484539052</v>
+      </c>
+      <c r="T3">
+        <v>0.756764849877408</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <v>0.0457</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>83.18636279102675</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1543743249693662</v>
+      </c>
+      <c r="C4">
+        <v>228.9727092264059</v>
+      </c>
+      <c r="D4">
+        <v>214.4497092264059</v>
+      </c>
+      <c r="E4">
+        <v>-2.573</v>
+      </c>
+      <c r="F4">
+        <v>4.577</v>
+      </c>
+      <c r="G4">
+        <v>19.1</v>
+      </c>
+      <c r="H4">
+        <v>221.7</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>24.2</v>
+      </c>
+      <c r="K4">
+        <v>15.5</v>
+      </c>
+      <c r="L4">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M4">
+        <v>0.2091689</v>
+      </c>
+      <c r="N4">
+        <v>8.490831099999999</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>8.490831099999999</v>
+      </c>
+      <c r="Q4">
+        <v>23.9908311</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1565921683360879</v>
+      </c>
+      <c r="T4">
+        <v>0.7644869401822795</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0.0457</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>41.59318139551338</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1544433249693662</v>
+      </c>
+      <c r="C5">
+        <v>226.5562551923919</v>
+      </c>
+      <c r="D5">
+        <v>214.3217551923919</v>
+      </c>
+      <c r="E5">
+        <v>-0.2845000000000004</v>
+      </c>
+      <c r="F5">
+        <v>6.8655</v>
+      </c>
+      <c r="G5">
+        <v>19.1</v>
+      </c>
+      <c r="H5">
+        <v>221.7</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>24.2</v>
+      </c>
+      <c r="K5">
+        <v>15.5</v>
+      </c>
+      <c r="L5">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M5">
+        <v>0.31375335</v>
+      </c>
+      <c r="N5">
+        <v>8.386246649999999</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>8.386246649999999</v>
+      </c>
+      <c r="Q5">
+        <v>23.88624665</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1578065205869754</v>
+      </c>
+      <c r="T5">
+        <v>0.7723682488439524</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0.0457</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>27.72878759700892</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1545123249693662</v>
+      </c>
+      <c r="C6">
+        <v>224.1399537579968</v>
+      </c>
+      <c r="D6">
+        <v>214.1939537579968</v>
+      </c>
+      <c r="E6">
+        <v>2.004</v>
+      </c>
+      <c r="F6">
+        <v>9.154</v>
+      </c>
+      <c r="G6">
+        <v>19.1</v>
+      </c>
+      <c r="H6">
+        <v>221.7</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>24.2</v>
+      </c>
+      <c r="K6">
+        <v>15.5</v>
+      </c>
+      <c r="L6">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M6">
+        <v>0.4183378</v>
+      </c>
+      <c r="N6">
+        <v>8.2816622</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>8.2816622</v>
+      </c>
+      <c r="Q6">
+        <v>23.7816622</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1590461718430898</v>
+      </c>
+      <c r="T6">
+        <v>0.7804137514360771</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0.0457</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>20.79659069775669</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1545813249693662</v>
+      </c>
+      <c r="C7">
+        <v>221.723804650395</v>
+      </c>
+      <c r="D7">
+        <v>214.066304650395</v>
+      </c>
+      <c r="E7">
+        <v>4.2925</v>
+      </c>
+      <c r="F7">
+        <v>11.4425</v>
+      </c>
+      <c r="G7">
+        <v>19.1</v>
+      </c>
+      <c r="H7">
+        <v>221.7</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>24.2</v>
+      </c>
+      <c r="K7">
+        <v>15.5</v>
+      </c>
+      <c r="L7">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M7">
+        <v>0.52292225</v>
+      </c>
+      <c r="N7">
+        <v>8.177077749999999</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>8.177077749999999</v>
+      </c>
+      <c r="Q7">
+        <v>23.67707775</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1603119210203854</v>
+      </c>
+      <c r="T7">
+        <v>0.7886286330301409</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0.0457</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>16.63727255820535</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1546503249693662</v>
+      </c>
+      <c r="C8">
+        <v>219.3078075974106</v>
+      </c>
+      <c r="D8">
+        <v>213.9388075974106</v>
+      </c>
+      <c r="E8">
+        <v>6.581</v>
+      </c>
+      <c r="F8">
+        <v>13.731</v>
+      </c>
+      <c r="G8">
+        <v>19.1</v>
+      </c>
+      <c r="H8">
+        <v>221.7</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>24.2</v>
+      </c>
+      <c r="K8">
+        <v>15.5</v>
+      </c>
+      <c r="L8">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M8">
+        <v>0.6275067000000001</v>
+      </c>
+      <c r="N8">
+        <v>8.0724933</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>8.0724933</v>
+      </c>
+      <c r="Q8">
+        <v>23.5724933</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1616046010312406</v>
+      </c>
+      <c r="T8">
+        <v>0.7970182993389722</v>
+      </c>
+      <c r="U8">
+        <v>0.0457</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0.0457</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>13.86439379850446</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1548313249693662</v>
+      </c>
+      <c r="C9">
+        <v>216.6855794064643</v>
+      </c>
+      <c r="D9">
+        <v>213.6050794064643</v>
+      </c>
+      <c r="E9">
+        <v>8.8695</v>
+      </c>
+      <c r="F9">
+        <v>16.0195</v>
+      </c>
+      <c r="G9">
+        <v>19.1</v>
+      </c>
+      <c r="H9">
+        <v>221.7</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>24.2</v>
+      </c>
+      <c r="K9">
+        <v>15.5</v>
+      </c>
+      <c r="L9">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M9">
+        <v>0.7577223500000001</v>
+      </c>
+      <c r="N9">
+        <v>7.942277649999999</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>7.942277649999999</v>
+      </c>
+      <c r="Q9">
+        <v>23.44227765</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1629250806122217</v>
+      </c>
+      <c r="T9">
+        <v>0.8055883885791761</v>
+      </c>
+      <c r="U9">
+        <v>0.0473</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>0.0473</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>11.4817782529445</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1552203249693662</v>
+      </c>
+      <c r="C10">
+        <v>213.6833520061072</v>
+      </c>
+      <c r="D10">
+        <v>212.8913520061072</v>
+      </c>
+      <c r="E10">
+        <v>11.158</v>
+      </c>
+      <c r="F10">
+        <v>18.308</v>
+      </c>
+      <c r="G10">
+        <v>19.1</v>
+      </c>
+      <c r="H10">
+        <v>221.7</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>24.2</v>
+      </c>
+      <c r="K10">
+        <v>15.5</v>
+      </c>
+      <c r="L10">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M10">
+        <v>0.9355388</v>
+      </c>
+      <c r="N10">
+        <v>7.7644612</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>7.7644612</v>
+      </c>
+      <c r="Q10">
+        <v>23.2644612</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1642742662710502</v>
+      </c>
+      <c r="T10">
+        <v>0.8143447841072107</v>
+      </c>
+      <c r="U10">
+        <v>0.0511</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0.0511</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>9.299453961717033</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1553433249693662</v>
+      </c>
+      <c r="C11">
+        <v>211.1701661538403</v>
+      </c>
+      <c r="D11">
+        <v>212.6666661538403</v>
+      </c>
+      <c r="E11">
+        <v>13.4465</v>
+      </c>
+      <c r="F11">
+        <v>20.5965</v>
+      </c>
+      <c r="G11">
+        <v>19.1</v>
+      </c>
+      <c r="H11">
+        <v>221.7</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>24.2</v>
+      </c>
+      <c r="K11">
+        <v>15.5</v>
+      </c>
+      <c r="L11">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M11">
+        <v>1.05248115</v>
+      </c>
+      <c r="N11">
+        <v>7.647518849999999</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>7.647518849999999</v>
+      </c>
+      <c r="Q11">
+        <v>23.14751885</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1656531043619409</v>
+      </c>
+      <c r="T11">
+        <v>0.8232936278886087</v>
+      </c>
+      <c r="U11">
+        <v>0.0511</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <v>0.0511</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>8.26618129930403</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1556563249693662</v>
+      </c>
+      <c r="C12">
+        <v>208.3120378814845</v>
+      </c>
+      <c r="D12">
+        <v>212.0970378814845</v>
+      </c>
+      <c r="E12">
+        <v>15.735</v>
+      </c>
+      <c r="F12">
+        <v>22.885</v>
+      </c>
+      <c r="G12">
+        <v>19.1</v>
+      </c>
+      <c r="H12">
+        <v>221.7</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>24.2</v>
+      </c>
+      <c r="K12">
+        <v>15.5</v>
+      </c>
+      <c r="L12">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M12">
+        <v>1.212905</v>
+      </c>
+      <c r="N12">
+        <v>7.487094999999999</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>7.487094999999999</v>
+      </c>
+      <c r="Q12">
+        <v>22.987095</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1670625832992958</v>
+      </c>
+      <c r="T12">
+        <v>0.8324413348651488</v>
+      </c>
+      <c r="U12">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>7.172861848207401</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1557983249693662</v>
+      </c>
+      <c r="C13">
+        <v>205.7661172783515</v>
+      </c>
+      <c r="D13">
+        <v>211.8396172783515</v>
+      </c>
+      <c r="E13">
+        <v>18.0235</v>
+      </c>
+      <c r="F13">
+        <v>25.1735</v>
+      </c>
+      <c r="G13">
+        <v>19.1</v>
+      </c>
+      <c r="H13">
+        <v>221.7</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>24.2</v>
+      </c>
+      <c r="K13">
+        <v>15.5</v>
+      </c>
+      <c r="L13">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M13">
+        <v>1.3341955</v>
+      </c>
+      <c r="N13">
+        <v>7.365804499999999</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>7.365804499999999</v>
+      </c>
+      <c r="Q13">
+        <v>22.8658045</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1685037359206362</v>
+      </c>
+      <c r="T13">
+        <v>0.8417946082905999</v>
+      </c>
+      <c r="U13">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>6.520783498370365</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1561803249693662</v>
+      </c>
+      <c r="C14">
+        <v>202.7882109930865</v>
+      </c>
+      <c r="D14">
+        <v>211.1502109930865</v>
+      </c>
+      <c r="E14">
+        <v>20.312</v>
+      </c>
+      <c r="F14">
+        <v>27.462</v>
+      </c>
+      <c r="G14">
+        <v>19.1</v>
+      </c>
+      <c r="H14">
+        <v>221.7</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>24.2</v>
+      </c>
+      <c r="K14">
+        <v>15.5</v>
+      </c>
+      <c r="L14">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M14">
+        <v>1.51041</v>
+      </c>
+      <c r="N14">
+        <v>7.189589999999999</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>7.189589999999999</v>
+      </c>
+      <c r="Q14">
+        <v>22.68959</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1699776420106434</v>
+      </c>
+      <c r="T14">
+        <v>0.8513604561120839</v>
+      </c>
+      <c r="U14">
+        <v>0.055</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0.055</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>5.76002542356049</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1563423249693662</v>
+      </c>
+      <c r="C15">
+        <v>200.2086980818667</v>
+      </c>
+      <c r="D15">
+        <v>210.8591980818667</v>
+      </c>
+      <c r="E15">
+        <v>22.6005</v>
+      </c>
+      <c r="F15">
+        <v>29.7505</v>
+      </c>
+      <c r="G15">
+        <v>19.1</v>
+      </c>
+      <c r="H15">
+        <v>221.7</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>24.2</v>
+      </c>
+      <c r="K15">
+        <v>15.5</v>
+      </c>
+      <c r="L15">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M15">
+        <v>1.6362775</v>
+      </c>
+      <c r="N15">
+        <v>7.063722499999999</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>7.063722499999999</v>
+      </c>
+      <c r="Q15">
+        <v>22.5637225</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1714854309992715</v>
+      </c>
+      <c r="T15">
+        <v>0.8611462084811883</v>
+      </c>
+      <c r="U15">
+        <v>0.055</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>0.055</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>5.316946544825067</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1565043249693662</v>
+      </c>
+      <c r="C16">
+        <v>197.6299862302787</v>
+      </c>
+      <c r="D16">
+        <v>210.5689862302787</v>
+      </c>
+      <c r="E16">
+        <v>24.889</v>
+      </c>
+      <c r="F16">
+        <v>32.039</v>
+      </c>
+      <c r="G16">
+        <v>19.1</v>
+      </c>
+      <c r="H16">
+        <v>221.7</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>24.2</v>
+      </c>
+      <c r="K16">
+        <v>15.5</v>
+      </c>
+      <c r="L16">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M16">
+        <v>1.762145</v>
+      </c>
+      <c r="N16">
+        <v>6.937854999999999</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>6.937854999999999</v>
+      </c>
+      <c r="Q16">
+        <v>22.437855</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1730282848481002</v>
+      </c>
+      <c r="T16">
+        <v>0.8711595364867837</v>
+      </c>
+      <c r="U16">
+        <v>0.055</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>0.055</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>4.937164648766133</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1566663249693662</v>
+      </c>
+      <c r="C17">
+        <v>195.0520721353014</v>
+      </c>
+      <c r="D17">
+        <v>210.2795721353015</v>
+      </c>
+      <c r="E17">
+        <v>27.1775</v>
+      </c>
+      <c r="F17">
+        <v>34.3275</v>
+      </c>
+      <c r="G17">
+        <v>19.1</v>
+      </c>
+      <c r="H17">
+        <v>221.7</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>24.2</v>
+      </c>
+      <c r="K17">
+        <v>15.5</v>
+      </c>
+      <c r="L17">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M17">
+        <v>1.8880125</v>
+      </c>
+      <c r="N17">
+        <v>6.811987499999999</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>6.811987499999999</v>
+      </c>
+      <c r="Q17">
+        <v>22.3119875</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1746074411404308</v>
+      </c>
+      <c r="T17">
+        <v>0.8814084722101575</v>
+      </c>
+      <c r="U17">
+        <v>0.055</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <v>0.055</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>4.608020338848391</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1574363249693662</v>
+      </c>
+      <c r="C18">
+        <v>191.3987686437403</v>
+      </c>
+      <c r="D18">
+        <v>208.9147686437403</v>
+      </c>
+      <c r="E18">
+        <v>29.466</v>
+      </c>
+      <c r="F18">
+        <v>36.616</v>
+      </c>
+      <c r="G18">
+        <v>19.1</v>
+      </c>
+      <c r="H18">
+        <v>221.7</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>24.2</v>
+      </c>
+      <c r="K18">
+        <v>15.5</v>
+      </c>
+      <c r="L18">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M18">
+        <v>2.1530208</v>
+      </c>
+      <c r="N18">
+        <v>6.546979199999999</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>6.546979199999999</v>
+      </c>
+      <c r="Q18">
+        <v>22.0469792</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1762241963921026</v>
+      </c>
+      <c r="T18">
+        <v>0.8919014302126593</v>
+      </c>
+      <c r="U18">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V18">
+        <v>0</v>
+      </c>
+      <c r="W18">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>4.040834161936568</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1583503249693662</v>
+      </c>
+      <c r="C19">
+        <v>187.5130492418749</v>
+      </c>
+      <c r="D19">
+        <v>207.3175492418749</v>
+      </c>
+      <c r="E19">
+        <v>31.7545</v>
+      </c>
+      <c r="F19">
+        <v>38.9045</v>
+      </c>
+      <c r="G19">
+        <v>19.1</v>
+      </c>
+      <c r="H19">
+        <v>221.7</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>24.2</v>
+      </c>
+      <c r="K19">
+        <v>15.5</v>
+      </c>
+      <c r="L19">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M19">
+        <v>2.4509835</v>
+      </c>
+      <c r="N19">
+        <v>6.2490165</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>6.2490165</v>
+      </c>
+      <c r="Q19">
+        <v>21.7490165</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.177879909601646</v>
+      </c>
+      <c r="T19">
+        <v>0.9026472305766674</v>
+      </c>
+      <c r="U19">
+        <v>0.063</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>0.063</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>3.549595499112907</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1598703249693662</v>
+      </c>
+      <c r="C20">
+        <v>182.6217423614327</v>
+      </c>
+      <c r="D20">
+        <v>204.7147423614327</v>
+      </c>
+      <c r="E20">
+        <v>34.043</v>
+      </c>
+      <c r="F20">
+        <v>41.193</v>
+      </c>
+      <c r="G20">
+        <v>19.1</v>
+      </c>
+      <c r="H20">
+        <v>221.7</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>24.2</v>
+      </c>
+      <c r="K20">
+        <v>15.5</v>
+      </c>
+      <c r="L20">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M20">
+        <v>2.8876293</v>
+      </c>
+      <c r="N20">
+        <v>5.8123707</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>5.8123707</v>
+      </c>
+      <c r="Q20">
+        <v>21.3123707</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1795760060602027</v>
+      </c>
+      <c r="T20">
+        <v>0.9136551236324804</v>
+      </c>
+      <c r="U20">
+        <v>0.0701</v>
+      </c>
+      <c r="V20">
+        <v>0</v>
+      </c>
+      <c r="W20">
+        <v>0.0701</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>3.01285209981766</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1642303249693662</v>
+      </c>
+      <c r="C21">
+        <v>173.2172895253555</v>
+      </c>
+      <c r="D21">
+        <v>197.5987895253554</v>
+      </c>
+      <c r="E21">
+        <v>36.3315</v>
+      </c>
+      <c r="F21">
+        <v>43.4815</v>
+      </c>
+      <c r="G21">
+        <v>19.1</v>
+      </c>
+      <c r="H21">
+        <v>221.7</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>24.2</v>
+      </c>
+      <c r="K21">
+        <v>15.5</v>
+      </c>
+      <c r="L21">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M21">
+        <v>3.9742091</v>
+      </c>
+      <c r="N21">
+        <v>4.7257909</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>4.7257909</v>
+      </c>
+      <c r="Q21">
+        <v>20.2257909</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.181313981443662</v>
+      </c>
+      <c r="T21">
+        <v>0.9249348165168318</v>
+      </c>
+      <c r="U21">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>2.189114810290178</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1647563249693662</v>
+      </c>
+      <c r="C22">
+        <v>170.1036069605607</v>
+      </c>
+      <c r="D22">
+        <v>196.7736069605607</v>
+      </c>
+      <c r="E22">
+        <v>38.62</v>
+      </c>
+      <c r="F22">
+        <v>45.77</v>
+      </c>
+      <c r="G22">
+        <v>19.1</v>
+      </c>
+      <c r="H22">
+        <v>221.7</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>24.2</v>
+      </c>
+      <c r="K22">
+        <v>15.5</v>
+      </c>
+      <c r="L22">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M22">
+        <v>4.183378</v>
+      </c>
+      <c r="N22">
+        <v>4.516621999999999</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>4.516621999999999</v>
+      </c>
+      <c r="Q22">
+        <v>20.016622</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1830954062117077</v>
+      </c>
+      <c r="T22">
+        <v>0.9364965017232924</v>
+      </c>
+      <c r="U22">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>2.079659069775669</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1697133249693662</v>
+      </c>
+      <c r="C23">
+        <v>160.3643240098432</v>
+      </c>
+      <c r="D23">
+        <v>189.3228240098432</v>
+      </c>
+      <c r="E23">
+        <v>40.9085</v>
+      </c>
+      <c r="F23">
+        <v>48.0585</v>
+      </c>
+      <c r="G23">
+        <v>19.1</v>
+      </c>
+      <c r="H23">
+        <v>221.7</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>24.2</v>
+      </c>
+      <c r="K23">
+        <v>15.5</v>
+      </c>
+      <c r="L23">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M23">
+        <v>5.406581249999999</v>
+      </c>
+      <c r="N23">
+        <v>3.29341875</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>3.29341875</v>
+      </c>
+      <c r="Q23">
+        <v>18.79341875</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1849219303409698</v>
+      </c>
+      <c r="T23">
+        <v>0.9483508878210556</v>
+      </c>
+      <c r="U23">
+        <v>0.1125</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0.1125</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>1.609149959597851</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1704503249693662</v>
+      </c>
+      <c r="C24">
+        <v>157.0159639500391</v>
+      </c>
+      <c r="D24">
+        <v>188.2629639500391</v>
+      </c>
+      <c r="E24">
+        <v>43.197</v>
+      </c>
+      <c r="F24">
+        <v>50.347</v>
+      </c>
+      <c r="G24">
+        <v>19.1</v>
+      </c>
+      <c r="H24">
+        <v>221.7</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>24.2</v>
+      </c>
+      <c r="K24">
+        <v>15.5</v>
+      </c>
+      <c r="L24">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M24">
+        <v>5.6640375</v>
+      </c>
+      <c r="N24">
+        <v>3.035962499999999</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>3.035962499999999</v>
+      </c>
+      <c r="Q24">
+        <v>18.5359625</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1867952884222643</v>
+      </c>
+      <c r="T24">
+        <v>0.9605092325367101</v>
+      </c>
+      <c r="U24">
+        <v>0.1125</v>
+      </c>
+      <c r="V24">
+        <v>0</v>
+      </c>
+      <c r="W24">
+        <v>0.1125</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>1.536006779616131</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1905303249693662</v>
+      </c>
+      <c r="C25">
+        <v>129.8127323900822</v>
+      </c>
+      <c r="D25">
+        <v>163.3482323900822</v>
+      </c>
+      <c r="E25">
+        <v>45.4855</v>
+      </c>
+      <c r="F25">
+        <v>52.6355</v>
+      </c>
+      <c r="G25">
+        <v>19.1</v>
+      </c>
+      <c r="H25">
+        <v>221.7</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>24.2</v>
+      </c>
+      <c r="K25">
+        <v>15.5</v>
+      </c>
+      <c r="L25">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M25">
+        <v>10.3481393</v>
+      </c>
+      <c r="N25">
+        <v>-1.6481393</v>
+      </c>
+      <c r="O25">
+        <v>-0</v>
+      </c>
+      <c r="P25">
+        <v>-1.6481393</v>
+      </c>
+      <c r="Q25">
+        <v>13.8518607</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.188717305155021</v>
+      </c>
+      <c r="T25">
+        <v>0.9729833784138102</v>
+      </c>
+      <c r="U25">
+        <v>0.1966</v>
+      </c>
+      <c r="V25">
+        <v>0</v>
+      </c>
+      <c r="W25">
+        <v>0.1966</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>0.8407308548697252</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1921083249693662</v>
+      </c>
+      <c r="C26">
+        <v>125.8428917925442</v>
+      </c>
+      <c r="D26">
+        <v>161.6668917925442</v>
+      </c>
+      <c r="E26">
+        <v>47.774</v>
+      </c>
+      <c r="F26">
+        <v>54.924</v>
+      </c>
+      <c r="G26">
+        <v>19.1</v>
+      </c>
+      <c r="H26">
+        <v>221.7</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>24.2</v>
+      </c>
+      <c r="K26">
+        <v>15.5</v>
+      </c>
+      <c r="L26">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M26">
+        <v>10.7980584</v>
+      </c>
+      <c r="N26">
+        <v>-2.098058400000001</v>
+      </c>
+      <c r="O26">
+        <v>-0</v>
+      </c>
+      <c r="P26">
+        <v>-2.098058400000001</v>
+      </c>
+      <c r="Q26">
+        <v>13.4019416</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1906899012754818</v>
+      </c>
+      <c r="T26">
+        <v>0.9857857912876762</v>
+      </c>
+      <c r="U26">
+        <v>0.1966</v>
+      </c>
+      <c r="V26">
+        <v>0</v>
+      </c>
+      <c r="W26">
+        <v>0.1966</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>0.8057004025834866</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1979863249693662</v>
+      </c>
+      <c r="C27">
+        <v>117.5847961621441</v>
+      </c>
+      <c r="D27">
+        <v>155.6972961621441</v>
+      </c>
+      <c r="E27">
+        <v>50.0625</v>
+      </c>
+      <c r="F27">
+        <v>57.2125</v>
+      </c>
+      <c r="G27">
+        <v>19.1</v>
+      </c>
+      <c r="H27">
+        <v>221.7</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>24.2</v>
+      </c>
+      <c r="K27">
+        <v>15.5</v>
+      </c>
+      <c r="L27">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M27">
+        <v>12.2320325</v>
+      </c>
+      <c r="N27">
+        <v>-3.5320325</v>
+      </c>
+      <c r="O27">
+        <v>-0</v>
+      </c>
+      <c r="P27">
+        <v>-3.5320325</v>
+      </c>
+      <c r="Q27">
+        <v>11.9679675</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1927150999591549</v>
+      </c>
+      <c r="T27">
+        <v>0.9989296018381785</v>
+      </c>
+      <c r="U27">
+        <v>0.2138</v>
+      </c>
+      <c r="V27">
+        <v>0</v>
+      </c>
+      <c r="W27">
+        <v>0.2138</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>0.7112472927128014</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1997363249693662</v>
+      </c>
+      <c r="C28">
+        <v>113.6032646583142</v>
+      </c>
+      <c r="D28">
+        <v>154.0042646583142</v>
+      </c>
+      <c r="E28">
+        <v>52.351</v>
+      </c>
+      <c r="F28">
+        <v>59.501</v>
+      </c>
+      <c r="G28">
+        <v>19.1</v>
+      </c>
+      <c r="H28">
+        <v>221.7</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>24.2</v>
+      </c>
+      <c r="K28">
+        <v>15.5</v>
+      </c>
+      <c r="L28">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M28">
+        <v>12.7213138</v>
+      </c>
+      <c r="N28">
+        <v>-4.0213138</v>
+      </c>
+      <c r="O28">
+        <v>-0</v>
+      </c>
+      <c r="P28">
+        <v>-4.0213138</v>
+      </c>
+      <c r="Q28">
+        <v>11.4786862</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1947950337423867</v>
+      </c>
+      <c r="T28">
+        <v>1.012428650511667</v>
+      </c>
+      <c r="U28">
+        <v>0.2138</v>
+      </c>
+      <c r="V28">
+        <v>0</v>
+      </c>
+      <c r="W28">
+        <v>0.2138</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>0.6838916276084629</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.2014863249693662</v>
+      </c>
+      <c r="C29">
+        <v>109.6581566846397</v>
+      </c>
+      <c r="D29">
+        <v>152.3476566846397</v>
+      </c>
+      <c r="E29">
+        <v>54.63950000000001</v>
+      </c>
+      <c r="F29">
+        <v>61.7895</v>
+      </c>
+      <c r="G29">
+        <v>19.1</v>
+      </c>
+      <c r="H29">
+        <v>221.7</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>24.2</v>
+      </c>
+      <c r="K29">
+        <v>15.5</v>
+      </c>
+      <c r="L29">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M29">
+        <v>13.2105951</v>
+      </c>
+      <c r="N29">
+        <v>-4.510595100000002</v>
+      </c>
+      <c r="O29">
+        <v>-0</v>
+      </c>
+      <c r="P29">
+        <v>-4.510595100000002</v>
+      </c>
+      <c r="Q29">
+        <v>10.9894049</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1969319520128304</v>
+      </c>
+      <c r="T29">
+        <v>1.026297536135115</v>
+      </c>
+      <c r="U29">
+        <v>0.2138</v>
+      </c>
+      <c r="V29">
+        <v>0</v>
+      </c>
+      <c r="W29">
+        <v>0.2138</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>0.6585623080674086</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.2032363249693662</v>
+      </c>
+      <c r="C30">
+        <v>105.7483093378914</v>
+      </c>
+      <c r="D30">
+        <v>150.7263093378914</v>
+      </c>
+      <c r="E30">
+        <v>56.928</v>
+      </c>
+      <c r="F30">
+        <v>64.078</v>
+      </c>
+      <c r="G30">
+        <v>19.1</v>
+      </c>
+      <c r="H30">
+        <v>221.7</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>24.2</v>
+      </c>
+      <c r="K30">
+        <v>15.5</v>
+      </c>
+      <c r="L30">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M30">
+        <v>13.6998764</v>
+      </c>
+      <c r="N30">
+        <v>-4.999876400000002</v>
+      </c>
+      <c r="O30">
+        <v>-0</v>
+      </c>
+      <c r="P30">
+        <v>-4.999876400000002</v>
+      </c>
+      <c r="Q30">
+        <v>10.5001236</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1991282291241197</v>
+      </c>
+      <c r="T30">
+        <v>1.040551668581436</v>
+      </c>
+      <c r="U30">
+        <v>0.2138</v>
+      </c>
+      <c r="V30">
+        <v>0</v>
+      </c>
+      <c r="W30">
+        <v>0.2138</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>0.6350422256364298</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.2049863249693662</v>
+      </c>
+      <c r="C31">
+        <v>101.8726086979475</v>
+      </c>
+      <c r="D31">
+        <v>149.1391086979475</v>
+      </c>
+      <c r="E31">
+        <v>59.21649999999999</v>
+      </c>
+      <c r="F31">
+        <v>66.36649999999999</v>
+      </c>
+      <c r="G31">
+        <v>19.1</v>
+      </c>
+      <c r="H31">
+        <v>221.7</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>24.2</v>
+      </c>
+      <c r="K31">
+        <v>15.5</v>
+      </c>
+      <c r="L31">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M31">
+        <v>14.1891577</v>
+      </c>
+      <c r="N31">
+        <v>-5.489157699999998</v>
+      </c>
+      <c r="O31">
+        <v>-0</v>
+      </c>
+      <c r="P31">
+        <v>-5.489157699999998</v>
+      </c>
+      <c r="Q31">
+        <v>10.0108423</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.2013863731962904</v>
+      </c>
+      <c r="T31">
+        <v>1.0552073258854</v>
+      </c>
+      <c r="U31">
+        <v>0.2138</v>
+      </c>
+      <c r="V31">
+        <v>0</v>
+      </c>
+      <c r="W31">
+        <v>0.2138</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>0.6131442178558634</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.2067363249693662</v>
+      </c>
+      <c r="C32">
+        <v>98.02998727562257</v>
+      </c>
+      <c r="D32">
+        <v>147.5849872756226</v>
+      </c>
+      <c r="E32">
+        <v>61.505</v>
+      </c>
+      <c r="F32">
+        <v>68.655</v>
+      </c>
+      <c r="G32">
+        <v>19.1</v>
+      </c>
+      <c r="H32">
+        <v>221.7</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>24.2</v>
+      </c>
+      <c r="K32">
+        <v>15.5</v>
+      </c>
+      <c r="L32">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M32">
+        <v>14.678439</v>
+      </c>
+      <c r="N32">
+        <v>-5.978439</v>
+      </c>
+      <c r="O32">
+        <v>-0</v>
+      </c>
+      <c r="P32">
+        <v>-5.978439</v>
+      </c>
+      <c r="Q32">
+        <v>9.521561</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.2037090356705231</v>
+      </c>
+      <c r="T32">
+        <v>1.070281716255191</v>
+      </c>
+      <c r="U32">
+        <v>0.2138</v>
+      </c>
+      <c r="V32">
+        <v>0</v>
+      </c>
+      <c r="W32">
+        <v>0.2138</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>0.5927060772606678</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.2084863249693661</v>
+      </c>
+      <c r="C33">
+        <v>94.21942161842264</v>
+      </c>
+      <c r="D33">
+        <v>146.0629216184226</v>
+      </c>
+      <c r="E33">
+        <v>63.7935</v>
+      </c>
+      <c r="F33">
+        <v>70.9435</v>
+      </c>
+      <c r="G33">
+        <v>19.1</v>
+      </c>
+      <c r="H33">
+        <v>221.7</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>24.2</v>
+      </c>
+      <c r="K33">
+        <v>15.5</v>
+      </c>
+      <c r="L33">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M33">
+        <v>15.1677203</v>
+      </c>
+      <c r="N33">
+        <v>-6.4677203</v>
+      </c>
+      <c r="O33">
+        <v>-0</v>
+      </c>
+      <c r="P33">
+        <v>-6.4677203</v>
+      </c>
+      <c r="Q33">
+        <v>9.0322797</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.2060990216947336</v>
+      </c>
+      <c r="T33">
+        <v>1.085793045476281</v>
+      </c>
+      <c r="U33">
+        <v>0.2138</v>
+      </c>
+      <c r="V33">
+        <v>0</v>
+      </c>
+      <c r="W33">
+        <v>0.2138</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>0.5735865263812914</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.2102363249693662</v>
+      </c>
+      <c r="C34">
+        <v>90.43993006294036</v>
+      </c>
+      <c r="D34">
+        <v>144.5719300629404</v>
+      </c>
+      <c r="E34">
+        <v>66.08199999999999</v>
+      </c>
+      <c r="F34">
+        <v>73.232</v>
+      </c>
+      <c r="G34">
+        <v>19.1</v>
+      </c>
+      <c r="H34">
+        <v>221.7</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>24.2</v>
+      </c>
+      <c r="K34">
+        <v>15.5</v>
+      </c>
+      <c r="L34">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M34">
+        <v>15.6570016</v>
+      </c>
+      <c r="N34">
+        <v>-6.9570016</v>
+      </c>
+      <c r="O34">
+        <v>-0</v>
+      </c>
+      <c r="P34">
+        <v>-6.9570016</v>
+      </c>
+      <c r="Q34">
+        <v>8.5429984</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.2085593014255385</v>
+      </c>
+      <c r="T34">
+        <v>1.101760590262697</v>
+      </c>
+      <c r="U34">
+        <v>0.2138</v>
+      </c>
+      <c r="V34">
+        <v>0</v>
+      </c>
+      <c r="W34">
+        <v>0.2138</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.555661947431876</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.2119863249693662</v>
+      </c>
+      <c r="C35">
+        <v>86.69057062351925</v>
+      </c>
+      <c r="D35">
+        <v>143.1110706235193</v>
+      </c>
+      <c r="E35">
+        <v>68.37049999999999</v>
+      </c>
+      <c r="F35">
+        <v>75.5205</v>
+      </c>
+      <c r="G35">
+        <v>19.1</v>
+      </c>
+      <c r="H35">
+        <v>221.7</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>24.2</v>
+      </c>
+      <c r="K35">
+        <v>15.5</v>
+      </c>
+      <c r="L35">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M35">
+        <v>16.1462829</v>
+      </c>
+      <c r="N35">
+        <v>-7.4462829</v>
+      </c>
+      <c r="O35">
+        <v>-0</v>
+      </c>
+      <c r="P35">
+        <v>-7.4462829</v>
+      </c>
+      <c r="Q35">
+        <v>8.0537171</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.2110930223423376</v>
+      </c>
+      <c r="T35">
+        <v>1.118204778177066</v>
+      </c>
+      <c r="U35">
+        <v>0.2138</v>
+      </c>
+      <c r="V35">
+        <v>0</v>
+      </c>
+      <c r="W35">
+        <v>0.2138</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.5388237066006072</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.2137363249693662</v>
+      </c>
+      <c r="C36">
+        <v>82.9704390076441</v>
+      </c>
+      <c r="D36">
+        <v>141.6794390076441</v>
+      </c>
+      <c r="E36">
+        <v>70.65899999999999</v>
+      </c>
+      <c r="F36">
+        <v>77.809</v>
+      </c>
+      <c r="G36">
+        <v>19.1</v>
+      </c>
+      <c r="H36">
+        <v>221.7</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>24.2</v>
+      </c>
+      <c r="K36">
+        <v>15.5</v>
+      </c>
+      <c r="L36">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M36">
+        <v>16.6355642</v>
+      </c>
+      <c r="N36">
+        <v>-7.935564199999998</v>
+      </c>
+      <c r="O36">
+        <v>-0</v>
+      </c>
+      <c r="P36">
+        <v>-7.935564199999998</v>
+      </c>
+      <c r="Q36">
+        <v>7.564435800000002</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.2137035226808579</v>
+      </c>
+      <c r="T36">
+        <v>1.135147274816112</v>
+      </c>
+      <c r="U36">
+        <v>0.2138</v>
+      </c>
+      <c r="V36">
+        <v>0</v>
+      </c>
+      <c r="W36">
+        <v>0.2138</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.5229759505241187</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.2154863249693662</v>
+      </c>
+      <c r="C37">
+        <v>79.27866674927115</v>
+      </c>
+      <c r="D37">
+        <v>140.2761667492712</v>
+      </c>
+      <c r="E37">
+        <v>72.94750000000001</v>
+      </c>
+      <c r="F37">
+        <v>80.09750000000001</v>
+      </c>
+      <c r="G37">
+        <v>19.1</v>
+      </c>
+      <c r="H37">
+        <v>221.7</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>24.2</v>
+      </c>
+      <c r="K37">
+        <v>15.5</v>
+      </c>
+      <c r="L37">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M37">
+        <v>17.1248455</v>
+      </c>
+      <c r="N37">
+        <v>-8.424845500000004</v>
+      </c>
+      <c r="O37">
+        <v>-0</v>
+      </c>
+      <c r="P37">
+        <v>-8.424845500000004</v>
+      </c>
+      <c r="Q37">
+        <v>7.075154499999996</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.2163943461067172</v>
+      </c>
+      <c r="T37">
+        <v>1.152611079044052</v>
+      </c>
+      <c r="U37">
+        <v>0.2138</v>
+      </c>
+      <c r="V37">
+        <v>0</v>
+      </c>
+      <c r="W37">
+        <v>0.2138</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.5080337805091437</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.2262363249693662</v>
+      </c>
+      <c r="C38">
+        <v>68.94493436007915</v>
+      </c>
+      <c r="D38">
+        <v>132.2309343600791</v>
+      </c>
+      <c r="E38">
+        <v>75.23599999999999</v>
+      </c>
+      <c r="F38">
+        <v>82.386</v>
+      </c>
+      <c r="G38">
+        <v>19.1</v>
+      </c>
+      <c r="H38">
+        <v>221.7</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>24.2</v>
+      </c>
+      <c r="K38">
+        <v>15.5</v>
+      </c>
+      <c r="L38">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M38">
+        <v>19.6737768</v>
+      </c>
+      <c r="N38">
+        <v>-10.9737768</v>
+      </c>
+      <c r="O38">
+        <v>-0</v>
+      </c>
+      <c r="P38">
+        <v>-10.9737768</v>
+      </c>
+      <c r="Q38">
+        <v>4.5262232</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.2191692577646347</v>
+      </c>
+      <c r="T38">
+        <v>1.170620627154116</v>
+      </c>
+      <c r="U38">
+        <v>0.2388</v>
+      </c>
+      <c r="V38">
+        <v>0</v>
+      </c>
+      <c r="W38">
+        <v>0.2388</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.442213007113103</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.2282363249693662</v>
+      </c>
+      <c r="C39">
+        <v>65.26038812257468</v>
+      </c>
+      <c r="D39">
+        <v>130.8348881225747</v>
+      </c>
+      <c r="E39">
+        <v>77.52449999999999</v>
+      </c>
+      <c r="F39">
+        <v>84.67449999999999</v>
+      </c>
+      <c r="G39">
+        <v>19.1</v>
+      </c>
+      <c r="H39">
+        <v>221.7</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>24.2</v>
+      </c>
+      <c r="K39">
+        <v>15.5</v>
+      </c>
+      <c r="L39">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M39">
+        <v>20.2202706</v>
+      </c>
+      <c r="N39">
+        <v>-11.5202706</v>
+      </c>
+      <c r="O39">
+        <v>-0</v>
+      </c>
+      <c r="P39">
+        <v>-11.5202706</v>
+      </c>
+      <c r="Q39">
+        <v>3.9797294</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.2220322618561368</v>
+      </c>
+      <c r="T39">
+        <v>1.189201906950213</v>
+      </c>
+      <c r="U39">
+        <v>0.2388</v>
+      </c>
+      <c r="V39">
+        <v>0</v>
+      </c>
+      <c r="W39">
+        <v>0.2388</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.4302613042181542</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.2302363249693662</v>
+      </c>
+      <c r="C40">
+        <v>61.60501181899423</v>
+      </c>
+      <c r="D40">
+        <v>129.4680118189942</v>
+      </c>
+      <c r="E40">
+        <v>79.81299999999999</v>
+      </c>
+      <c r="F40">
+        <v>86.96299999999999</v>
+      </c>
+      <c r="G40">
+        <v>19.1</v>
+      </c>
+      <c r="H40">
+        <v>221.7</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>24.2</v>
+      </c>
+      <c r="K40">
+        <v>15.5</v>
+      </c>
+      <c r="L40">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M40">
+        <v>20.7667644</v>
+      </c>
+      <c r="N40">
+        <v>-12.0667644</v>
+      </c>
+      <c r="O40">
+        <v>-0</v>
+      </c>
+      <c r="P40">
+        <v>-12.0667644</v>
+      </c>
+      <c r="Q40">
+        <v>3.4332356</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.2249876209183325</v>
+      </c>
+      <c r="T40">
+        <v>1.208382582868764</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>0</v>
+      </c>
+      <c r="W40">
+        <v>0.2388</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.4189386383176764</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.2322363249693662</v>
+      </c>
+      <c r="C41">
+        <v>57.97790065752288</v>
+      </c>
+      <c r="D41">
+        <v>128.1294006575229</v>
+      </c>
+      <c r="E41">
+        <v>82.1015</v>
+      </c>
+      <c r="F41">
+        <v>89.25150000000001</v>
+      </c>
+      <c r="G41">
+        <v>19.1</v>
+      </c>
+      <c r="H41">
+        <v>221.7</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>24.2</v>
+      </c>
+      <c r="K41">
+        <v>15.5</v>
+      </c>
+      <c r="L41">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M41">
+        <v>21.3132582</v>
+      </c>
+      <c r="N41">
+        <v>-12.6132582</v>
+      </c>
+      <c r="O41">
+        <v>-0</v>
+      </c>
+      <c r="P41">
+        <v>-12.6132582</v>
+      </c>
+      <c r="Q41">
+        <v>2.886741799999996</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.2280398769989609</v>
+      </c>
+      <c r="T41">
+        <v>1.228192133407596</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>0</v>
+      </c>
+      <c r="W41">
+        <v>0.2388</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.4081966219505565</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.2342363249693662</v>
+      </c>
+      <c r="C42">
+        <v>54.37818688313776</v>
+      </c>
+      <c r="D42">
+        <v>126.8181868831378</v>
+      </c>
+      <c r="E42">
+        <v>84.39</v>
+      </c>
+      <c r="F42">
+        <v>91.54000000000001</v>
+      </c>
+      <c r="G42">
+        <v>19.1</v>
+      </c>
+      <c r="H42">
+        <v>221.7</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>24.2</v>
+      </c>
+      <c r="K42">
+        <v>15.5</v>
+      </c>
+      <c r="L42">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M42">
+        <v>21.859752</v>
+      </c>
+      <c r="N42">
+        <v>-13.159752</v>
+      </c>
+      <c r="O42">
+        <v>-0</v>
+      </c>
+      <c r="P42">
+        <v>-13.159752</v>
+      </c>
+      <c r="Q42">
+        <v>2.340247999999995</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.2311938749489437</v>
+      </c>
+      <c r="T42">
+        <v>1.248662002297723</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>0</v>
+      </c>
+      <c r="W42">
+        <v>0.2388</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.3979917064017926</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.2362363249693662</v>
+      </c>
+      <c r="C43">
+        <v>50.80503790172243</v>
+      </c>
+      <c r="D43">
+        <v>125.5335379017224</v>
+      </c>
+      <c r="E43">
+        <v>86.6785</v>
+      </c>
+      <c r="F43">
+        <v>93.82850000000001</v>
+      </c>
+      <c r="G43">
+        <v>19.1</v>
+      </c>
+      <c r="H43">
+        <v>221.7</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>24.2</v>
+      </c>
+      <c r="K43">
+        <v>15.5</v>
+      </c>
+      <c r="L43">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M43">
+        <v>22.4062458</v>
+      </c>
+      <c r="N43">
+        <v>-13.7062458</v>
+      </c>
+      <c r="O43">
+        <v>-0</v>
+      </c>
+      <c r="P43">
+        <v>-13.7062458</v>
+      </c>
+      <c r="Q43">
+        <v>1.793754199999999</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.2344547880836715</v>
+      </c>
+      <c r="T43">
+        <v>1.269825765048532</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>0</v>
+      </c>
+      <c r="W43">
+        <v>0.2388</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.388284591611505</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.2382363249693662</v>
+      </c>
+      <c r="C44">
+        <v>47.25765451705314</v>
+      </c>
+      <c r="D44">
+        <v>124.2746545170531</v>
+      </c>
+      <c r="E44">
+        <v>88.96699999999998</v>
+      </c>
+      <c r="F44">
+        <v>96.11699999999999</v>
+      </c>
+      <c r="G44">
+        <v>19.1</v>
+      </c>
+      <c r="H44">
+        <v>221.7</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>24.2</v>
+      </c>
+      <c r="K44">
+        <v>15.5</v>
+      </c>
+      <c r="L44">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M44">
+        <v>22.9527396</v>
+      </c>
+      <c r="N44">
+        <v>-14.2527396</v>
+      </c>
+      <c r="O44">
+        <v>-0</v>
+      </c>
+      <c r="P44">
+        <v>-14.2527396</v>
+      </c>
+      <c r="Q44">
+        <v>1.247260400000002</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.2378281464989072</v>
+      </c>
+      <c r="T44">
+        <v>1.291719312721783</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>0</v>
+      </c>
+      <c r="W44">
+        <v>0.2388</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.3790397203826597</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.2402363249693662</v>
+      </c>
+      <c r="C45">
+        <v>43.73526927281083</v>
+      </c>
+      <c r="D45">
+        <v>123.0407692728108</v>
+      </c>
+      <c r="E45">
+        <v>91.25549999999998</v>
+      </c>
+      <c r="F45">
+        <v>98.40549999999999</v>
+      </c>
+      <c r="G45">
+        <v>19.1</v>
+      </c>
+      <c r="H45">
+        <v>221.7</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>24.2</v>
+      </c>
+      <c r="K45">
+        <v>15.5</v>
+      </c>
+      <c r="L45">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M45">
+        <v>23.4992334</v>
+      </c>
+      <c r="N45">
+        <v>-14.7992334</v>
+      </c>
+      <c r="O45">
+        <v>-0</v>
+      </c>
+      <c r="P45">
+        <v>-14.7992334</v>
+      </c>
+      <c r="Q45">
+        <v>0.7007666000000015</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.2413198683673091</v>
+      </c>
+      <c r="T45">
+        <v>1.314381055050235</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>0</v>
+      </c>
+      <c r="W45">
+        <v>0.2388</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.3702248431644583</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.2422363249693662</v>
+      </c>
+      <c r="C46">
+        <v>40.23714489239261</v>
+      </c>
+      <c r="D46">
+        <v>121.8311448923926</v>
+      </c>
+      <c r="E46">
+        <v>93.544</v>
+      </c>
+      <c r="F46">
+        <v>100.694</v>
+      </c>
+      <c r="G46">
+        <v>19.1</v>
+      </c>
+      <c r="H46">
+        <v>221.7</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>24.2</v>
+      </c>
+      <c r="K46">
+        <v>15.5</v>
+      </c>
+      <c r="L46">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M46">
+        <v>24.0457272</v>
+      </c>
+      <c r="N46">
+        <v>-15.3457272</v>
+      </c>
+      <c r="O46">
+        <v>-0</v>
+      </c>
+      <c r="P46">
+        <v>-15.3457272</v>
+      </c>
+      <c r="Q46">
+        <v>0.1542727999999975</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.2449362945881539</v>
+      </c>
+      <c r="T46">
+        <v>1.337852145318989</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>0</v>
+      </c>
+      <c r="W46">
+        <v>0.2388</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.3618106421834478</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.2442363249693662</v>
+      </c>
+      <c r="C47">
+        <v>36.76257280985745</v>
+      </c>
+      <c r="D47">
+        <v>120.6450728098575</v>
+      </c>
+      <c r="E47">
+        <v>95.8325</v>
+      </c>
+      <c r="F47">
+        <v>102.9825</v>
+      </c>
+      <c r="G47">
+        <v>19.1</v>
+      </c>
+      <c r="H47">
+        <v>221.7</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>24.2</v>
+      </c>
+      <c r="K47">
+        <v>15.5</v>
+      </c>
+      <c r="L47">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M47">
+        <v>24.592221</v>
+      </c>
+      <c r="N47">
+        <v>-15.892221</v>
+      </c>
+      <c r="O47">
+        <v>-0</v>
+      </c>
+      <c r="P47">
+        <v>-15.892221</v>
+      </c>
+      <c r="Q47">
+        <v>-0.3922210000000028</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.2486842272170294</v>
+      </c>
+      <c r="T47">
+        <v>1.362176729779334</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>0</v>
+      </c>
+      <c r="W47">
+        <v>0.2388</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.3537704056904823</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.2462363249693662</v>
+      </c>
+      <c r="C48">
+        <v>33.31087178585479</v>
+      </c>
+      <c r="D48">
+        <v>119.4818717858548</v>
+      </c>
+      <c r="E48">
+        <v>98.121</v>
+      </c>
+      <c r="F48">
+        <v>105.271</v>
+      </c>
+      <c r="G48">
+        <v>19.1</v>
+      </c>
+      <c r="H48">
+        <v>221.7</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>24.2</v>
+      </c>
+      <c r="K48">
+        <v>15.5</v>
+      </c>
+      <c r="L48">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M48">
+        <v>25.1387148</v>
+      </c>
+      <c r="N48">
+        <v>-16.4387148</v>
+      </c>
+      <c r="O48">
+        <v>-0</v>
+      </c>
+      <c r="P48">
+        <v>-16.4387148</v>
+      </c>
+      <c r="Q48">
+        <v>-0.9387148000000032</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.252570972165493</v>
+      </c>
+      <c r="T48">
+        <v>1.387402224775248</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>0</v>
+      </c>
+      <c r="W48">
+        <v>0.2388</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.3460797446972109</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.2482363249693662</v>
+      </c>
+      <c r="C49">
+        <v>29.8813866028563</v>
+      </c>
+      <c r="D49">
+        <v>118.3408866028563</v>
+      </c>
+      <c r="E49">
+        <v>100.4095</v>
+      </c>
+      <c r="F49">
+        <v>107.5595</v>
+      </c>
+      <c r="G49">
+        <v>19.1</v>
+      </c>
+      <c r="H49">
+        <v>221.7</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>24.2</v>
+      </c>
+      <c r="K49">
+        <v>15.5</v>
+      </c>
+      <c r="L49">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M49">
+        <v>25.6852086</v>
+      </c>
+      <c r="N49">
+        <v>-16.9852086</v>
+      </c>
+      <c r="O49">
+        <v>-0</v>
+      </c>
+      <c r="P49">
+        <v>-16.9852086</v>
+      </c>
+      <c r="Q49">
+        <v>-1.485208600000004</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.2566043867346532</v>
+      </c>
+      <c r="T49">
+        <v>1.413579625242706</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>0</v>
+      </c>
+      <c r="W49">
+        <v>0.2388</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.338716345873866</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.2502363249693662</v>
+      </c>
+      <c r="C50">
+        <v>26.47348683443899</v>
+      </c>
+      <c r="D50">
+        <v>117.221486834439</v>
+      </c>
+      <c r="E50">
+        <v>102.698</v>
+      </c>
+      <c r="F50">
+        <v>109.848</v>
+      </c>
+      <c r="G50">
+        <v>19.1</v>
+      </c>
+      <c r="H50">
+        <v>221.7</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>24.2</v>
+      </c>
+      <c r="K50">
+        <v>15.5</v>
+      </c>
+      <c r="L50">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M50">
+        <v>26.2317024</v>
+      </c>
+      <c r="N50">
+        <v>-17.5317024</v>
+      </c>
+      <c r="O50">
+        <v>-0</v>
+      </c>
+      <c r="P50">
+        <v>-17.5317024</v>
+      </c>
+      <c r="Q50">
+        <v>-2.0317024</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.2607929326333965</v>
+      </c>
+      <c r="T50">
+        <v>1.440763848805065</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>0</v>
+      </c>
+      <c r="W50">
+        <v>0.2388</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.3316597553348272</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.2522363249693662</v>
+      </c>
+      <c r="C51">
+        <v>23.08656568376311</v>
+      </c>
+      <c r="D51">
+        <v>116.1230656837631</v>
+      </c>
+      <c r="E51">
+        <v>104.9865</v>
+      </c>
+      <c r="F51">
+        <v>112.1365</v>
+      </c>
+      <c r="G51">
+        <v>19.1</v>
+      </c>
+      <c r="H51">
+        <v>221.7</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>24.2</v>
+      </c>
+      <c r="K51">
+        <v>15.5</v>
+      </c>
+      <c r="L51">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M51">
+        <v>26.7781962</v>
+      </c>
+      <c r="N51">
+        <v>-18.0781962</v>
+      </c>
+      <c r="O51">
+        <v>-0</v>
+      </c>
+      <c r="P51">
+        <v>-18.0781962</v>
+      </c>
+      <c r="Q51">
+        <v>-2.578196200000001</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.2651457352340513</v>
+      </c>
+      <c r="T51">
+        <v>1.469014120350262</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0</v>
+      </c>
+      <c r="W51">
+        <v>0.2388</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.3248911888994226</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.2542363249693662</v>
+      </c>
+      <c r="C52">
+        <v>19.72003888674759</v>
+      </c>
+      <c r="D52">
+        <v>115.0450388867476</v>
+      </c>
+      <c r="E52">
+        <v>107.275</v>
+      </c>
+      <c r="F52">
+        <v>114.425</v>
+      </c>
+      <c r="G52">
+        <v>19.1</v>
+      </c>
+      <c r="H52">
+        <v>221.7</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>24.2</v>
+      </c>
+      <c r="K52">
+        <v>15.5</v>
+      </c>
+      <c r="L52">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M52">
+        <v>27.32469</v>
+      </c>
+      <c r="N52">
+        <v>-18.62469</v>
+      </c>
+      <c r="O52">
+        <v>-0</v>
+      </c>
+      <c r="P52">
+        <v>-18.62469</v>
+      </c>
+      <c r="Q52">
+        <v>-3.124690000000001</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.2696726499387324</v>
+      </c>
+      <c r="T52">
+        <v>1.498394402757268</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0</v>
+      </c>
+      <c r="W52">
+        <v>0.2388</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.3183933651214341</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.2562363249693662</v>
+      </c>
+      <c r="C53">
+        <v>16.3733436757776</v>
+      </c>
+      <c r="D53">
+        <v>113.9868436757776</v>
+      </c>
+      <c r="E53">
+        <v>109.5635</v>
+      </c>
+      <c r="F53">
+        <v>116.7135</v>
+      </c>
+      <c r="G53">
+        <v>19.1</v>
+      </c>
+      <c r="H53">
+        <v>221.7</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>24.2</v>
+      </c>
+      <c r="K53">
+        <v>15.5</v>
+      </c>
+      <c r="L53">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M53">
+        <v>27.8711838</v>
+      </c>
+      <c r="N53">
+        <v>-19.1711838</v>
+      </c>
+      <c r="O53">
+        <v>-0</v>
+      </c>
+      <c r="P53">
+        <v>-19.1711838</v>
+      </c>
+      <c r="Q53">
+        <v>-3.671183800000001</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.2743843366721759</v>
+      </c>
+      <c r="T53">
+        <v>1.528973880364559</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0</v>
+      </c>
+      <c r="W53">
+        <v>0.2388</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.3121503579621903</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.2582363249693662</v>
+      </c>
+      <c r="C54">
+        <v>13.04593780008277</v>
+      </c>
+      <c r="D54">
+        <v>112.9479378000828</v>
+      </c>
+      <c r="E54">
+        <v>111.852</v>
+      </c>
+      <c r="F54">
+        <v>119.002</v>
+      </c>
+      <c r="G54">
+        <v>19.1</v>
+      </c>
+      <c r="H54">
+        <v>221.7</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>24.2</v>
+      </c>
+      <c r="K54">
+        <v>15.5</v>
+      </c>
+      <c r="L54">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M54">
+        <v>28.4176776</v>
+      </c>
+      <c r="N54">
+        <v>-19.7176776</v>
+      </c>
+      <c r="O54">
+        <v>-0</v>
+      </c>
+      <c r="P54">
+        <v>-19.7176776</v>
+      </c>
+      <c r="Q54">
+        <v>-4.217677600000002</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.2792923436861796</v>
+      </c>
+      <c r="T54">
+        <v>1.560827502872154</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0</v>
+      </c>
+      <c r="W54">
+        <v>0.2388</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.3061474664629174</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.2602363249693662</v>
+      </c>
+      <c r="C55">
+        <v>9.737298599202262</v>
+      </c>
+      <c r="D55">
+        <v>111.9277985992023</v>
+      </c>
+      <c r="E55">
+        <v>114.1405</v>
+      </c>
+      <c r="F55">
+        <v>121.2905</v>
+      </c>
+      <c r="G55">
+        <v>19.1</v>
+      </c>
+      <c r="H55">
+        <v>221.7</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>24.2</v>
+      </c>
+      <c r="K55">
+        <v>15.5</v>
+      </c>
+      <c r="L55">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M55">
+        <v>28.96417140000001</v>
+      </c>
+      <c r="N55">
+        <v>-20.26417140000001</v>
+      </c>
+      <c r="O55">
+        <v>-0</v>
+      </c>
+      <c r="P55">
+        <v>-20.26417140000001</v>
+      </c>
+      <c r="Q55">
+        <v>-4.764171400000006</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.2844092020624812</v>
+      </c>
+      <c r="T55">
+        <v>1.594036598677944</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0</v>
+      </c>
+      <c r="W55">
+        <v>0.2388</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.3003710991711642</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.2622363249693662</v>
+      </c>
+      <c r="C56">
+        <v>6.446922126211177</v>
+      </c>
+      <c r="D56">
+        <v>110.9259221262112</v>
+      </c>
+      <c r="E56">
+        <v>116.429</v>
+      </c>
+      <c r="F56">
+        <v>123.579</v>
+      </c>
+      <c r="G56">
+        <v>19.1</v>
+      </c>
+      <c r="H56">
+        <v>221.7</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>24.2</v>
+      </c>
+      <c r="K56">
+        <v>15.5</v>
+      </c>
+      <c r="L56">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M56">
+        <v>29.5106652</v>
+      </c>
+      <c r="N56">
+        <v>-20.8106652</v>
+      </c>
+      <c r="O56">
+        <v>-0</v>
+      </c>
+      <c r="P56">
+        <v>-20.8106652</v>
+      </c>
+      <c r="Q56">
+        <v>-5.310665200000003</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.2897485325421004</v>
+      </c>
+      <c r="T56">
+        <v>1.628689568214421</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0</v>
+      </c>
+      <c r="W56">
+        <v>0.2388</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.2948086714087352</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.2642363249693662</v>
+      </c>
+      <c r="C57">
+        <v>3.174322317617424</v>
+      </c>
+      <c r="D57">
+        <v>109.9418223176174</v>
+      </c>
+      <c r="E57">
+        <v>118.7175</v>
+      </c>
+      <c r="F57">
+        <v>125.8675</v>
+      </c>
+      <c r="G57">
+        <v>19.1</v>
+      </c>
+      <c r="H57">
+        <v>221.7</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>24.2</v>
+      </c>
+      <c r="K57">
+        <v>15.5</v>
+      </c>
+      <c r="L57">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M57">
+        <v>30.057159</v>
+      </c>
+      <c r="N57">
+        <v>-21.357159</v>
+      </c>
+      <c r="O57">
+        <v>-0</v>
+      </c>
+      <c r="P57">
+        <v>-21.357159</v>
+      </c>
+      <c r="Q57">
+        <v>-5.857159000000003</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.2953251665985915</v>
+      </c>
+      <c r="T57">
+        <v>1.664882669730298</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0</v>
+      </c>
+      <c r="W57">
+        <v>0.2388</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.2894485137467583</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.2662363249693662</v>
+      </c>
+      <c r="C58">
+        <v>-0.0809697929429376</v>
+      </c>
+      <c r="D58">
+        <v>108.9750302070571</v>
+      </c>
+      <c r="E58">
+        <v>121.006</v>
+      </c>
+      <c r="F58">
+        <v>128.156</v>
+      </c>
+      <c r="G58">
+        <v>19.1</v>
+      </c>
+      <c r="H58">
+        <v>221.7</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>24.2</v>
+      </c>
+      <c r="K58">
+        <v>15.5</v>
+      </c>
+      <c r="L58">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M58">
+        <v>30.6036528</v>
+      </c>
+      <c r="N58">
+        <v>-21.9036528</v>
+      </c>
+      <c r="O58">
+        <v>-0</v>
+      </c>
+      <c r="P58">
+        <v>-21.9036528</v>
+      </c>
+      <c r="Q58">
+        <v>-6.403652800000003</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.3011552840212868</v>
+      </c>
+      <c r="T58">
+        <v>1.702720912224168</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0</v>
+      </c>
+      <c r="W58">
+        <v>0.2388</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.2842797902869947</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2682363249693662</v>
+      </c>
+      <c r="C59">
+        <v>-3.319406819885899</v>
+      </c>
+      <c r="D59">
+        <v>108.0250931801141</v>
+      </c>
+      <c r="E59">
+        <v>123.2945</v>
+      </c>
+      <c r="F59">
+        <v>130.4445</v>
+      </c>
+      <c r="G59">
+        <v>19.1</v>
+      </c>
+      <c r="H59">
+        <v>221.7</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>24.2</v>
+      </c>
+      <c r="K59">
+        <v>15.5</v>
+      </c>
+      <c r="L59">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M59">
+        <v>31.1501466</v>
+      </c>
+      <c r="N59">
+        <v>-22.4501466</v>
+      </c>
+      <c r="O59">
+        <v>-0</v>
+      </c>
+      <c r="P59">
+        <v>-22.4501466</v>
+      </c>
+      <c r="Q59">
+        <v>-6.950146600000004</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.3072565696962005</v>
+      </c>
+      <c r="T59">
+        <v>1.742319072973568</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0</v>
+      </c>
+      <c r="W59">
+        <v>0.2388</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.2792924255451176</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2702363249693662</v>
+      </c>
+      <c r="C60">
+        <v>-6.541425732220944</v>
+      </c>
+      <c r="D60">
+        <v>107.091574267779</v>
+      </c>
+      <c r="E60">
+        <v>125.583</v>
+      </c>
+      <c r="F60">
+        <v>132.733</v>
+      </c>
+      <c r="G60">
+        <v>19.1</v>
+      </c>
+      <c r="H60">
+        <v>221.7</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>24.2</v>
+      </c>
+      <c r="K60">
+        <v>15.5</v>
+      </c>
+      <c r="L60">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M60">
+        <v>31.6966404</v>
+      </c>
+      <c r="N60">
+        <v>-22.9966404</v>
+      </c>
+      <c r="O60">
+        <v>-0</v>
+      </c>
+      <c r="P60">
+        <v>-22.9966404</v>
+      </c>
+      <c r="Q60">
+        <v>-7.496640399999997</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.3136483927842051</v>
+      </c>
+      <c r="T60">
+        <v>1.783802860425318</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0</v>
+      </c>
+      <c r="W60">
+        <v>0.2388</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.2744770388977881</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2722363249693661</v>
+      </c>
+      <c r="C61">
+        <v>-9.747448523773045</v>
+      </c>
+      <c r="D61">
+        <v>106.1740514762269</v>
+      </c>
+      <c r="E61">
+        <v>127.8715</v>
+      </c>
+      <c r="F61">
+        <v>135.0215</v>
+      </c>
+      <c r="G61">
+        <v>19.1</v>
+      </c>
+      <c r="H61">
+        <v>221.7</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>24.2</v>
+      </c>
+      <c r="K61">
+        <v>15.5</v>
+      </c>
+      <c r="L61">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M61">
+        <v>32.2431342</v>
+      </c>
+      <c r="N61">
+        <v>-23.5431342</v>
+      </c>
+      <c r="O61">
+        <v>-0</v>
+      </c>
+      <c r="P61">
+        <v>-23.5431342</v>
+      </c>
+      <c r="Q61">
+        <v>-8.043134200000001</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.3203520121204053</v>
+      </c>
+      <c r="T61">
+        <v>1.82731024726496</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0</v>
+      </c>
+      <c r="W61">
+        <v>0.2388</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.2698248856961306</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2742363249693662</v>
+      </c>
+      <c r="C62">
+        <v>-12.93788284924338</v>
+      </c>
+      <c r="D62">
+        <v>105.2721171507566</v>
+      </c>
+      <c r="E62">
+        <v>130.16</v>
+      </c>
+      <c r="F62">
+        <v>137.31</v>
+      </c>
+      <c r="G62">
+        <v>19.1</v>
+      </c>
+      <c r="H62">
+        <v>221.7</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>24.2</v>
+      </c>
+      <c r="K62">
+        <v>15.5</v>
+      </c>
+      <c r="L62">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M62">
+        <v>32.789628</v>
+      </c>
+      <c r="N62">
+        <v>-24.089628</v>
+      </c>
+      <c r="O62">
+        <v>-0</v>
+      </c>
+      <c r="P62">
+        <v>-24.089628</v>
+      </c>
+      <c r="Q62">
+        <v>-8.589628000000001</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.3273908124234154</v>
+      </c>
+      <c r="T62">
+        <v>1.872993003446585</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0</v>
+      </c>
+      <c r="W62">
+        <v>0.2388</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.2653278042678617</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2762363249693662</v>
+      </c>
+      <c r="C63">
+        <v>-16.11312262812379</v>
+      </c>
+      <c r="D63">
+        <v>104.3853773718762</v>
+      </c>
+      <c r="E63">
+        <v>132.4485</v>
+      </c>
+      <c r="F63">
+        <v>139.5985</v>
+      </c>
+      <c r="G63">
+        <v>19.1</v>
+      </c>
+      <c r="H63">
+        <v>221.7</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>24.2</v>
+      </c>
+      <c r="K63">
+        <v>15.5</v>
+      </c>
+      <c r="L63">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M63">
+        <v>33.3361218</v>
+      </c>
+      <c r="N63">
+        <v>-24.6361218</v>
+      </c>
+      <c r="O63">
+        <v>-0</v>
+      </c>
+      <c r="P63">
+        <v>-24.6361218</v>
+      </c>
+      <c r="Q63">
+        <v>-9.136121800000002</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.3347905768445287</v>
+      </c>
+      <c r="T63">
+        <v>1.92101846507342</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0</v>
+      </c>
+      <c r="W63">
+        <v>0.2388</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.260978168132323</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2782363249693662</v>
+      </c>
+      <c r="C64">
+        <v>-19.27354861834462</v>
+      </c>
+      <c r="D64">
+        <v>103.5134513816554</v>
+      </c>
+      <c r="E64">
+        <v>134.737</v>
+      </c>
+      <c r="F64">
+        <v>141.887</v>
+      </c>
+      <c r="G64">
+        <v>19.1</v>
+      </c>
+      <c r="H64">
+        <v>221.7</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>24.2</v>
+      </c>
+      <c r="K64">
+        <v>15.5</v>
+      </c>
+      <c r="L64">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M64">
+        <v>33.8826156</v>
+      </c>
+      <c r="N64">
+        <v>-25.1826156</v>
+      </c>
+      <c r="O64">
+        <v>-0</v>
+      </c>
+      <c r="P64">
+        <v>-25.1826156</v>
+      </c>
+      <c r="Q64">
+        <v>-9.682615600000002</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.3425798025509637</v>
+      </c>
+      <c r="T64">
+        <v>1.971571582575352</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0</v>
+      </c>
+      <c r="W64">
+        <v>0.2388</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.2567688428398662</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2802363249693662</v>
+      </c>
+      <c r="C65">
+        <v>-22.41952896141055</v>
+      </c>
+      <c r="D65">
+        <v>102.6559710385894</v>
+      </c>
+      <c r="E65">
+        <v>137.0255</v>
+      </c>
+      <c r="F65">
+        <v>144.1755</v>
+      </c>
+      <c r="G65">
+        <v>19.1</v>
+      </c>
+      <c r="H65">
+        <v>221.7</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>24.2</v>
+      </c>
+      <c r="K65">
+        <v>15.5</v>
+      </c>
+      <c r="L65">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M65">
+        <v>34.4291094</v>
+      </c>
+      <c r="N65">
+        <v>-25.7291094</v>
+      </c>
+      <c r="O65">
+        <v>-0</v>
+      </c>
+      <c r="P65">
+        <v>-25.7291094</v>
+      </c>
+      <c r="Q65">
+        <v>-10.2291094</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.3507900674847734</v>
+      </c>
+      <c r="T65">
+        <v>2.024857301023335</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0</v>
+      </c>
+      <c r="W65">
+        <v>0.2388</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.2526931469217731</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2822363249693662</v>
+      </c>
+      <c r="C66">
+        <v>-25.55141970066452</v>
+      </c>
+      <c r="D66">
+        <v>101.8125802993355</v>
+      </c>
+      <c r="E66">
+        <v>139.314</v>
+      </c>
+      <c r="F66">
+        <v>146.464</v>
+      </c>
+      <c r="G66">
+        <v>19.1</v>
+      </c>
+      <c r="H66">
+        <v>221.7</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>24.2</v>
+      </c>
+      <c r="K66">
+        <v>15.5</v>
+      </c>
+      <c r="L66">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M66">
+        <v>34.9756032</v>
+      </c>
+      <c r="N66">
+        <v>-26.2756032</v>
+      </c>
+      <c r="O66">
+        <v>-0</v>
+      </c>
+      <c r="P66">
+        <v>-26.2756032</v>
+      </c>
+      <c r="Q66">
+        <v>-10.7756032</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.3594564582482394</v>
+      </c>
+      <c r="T66">
+        <v>2.081103337162872</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0</v>
+      </c>
+      <c r="W66">
+        <v>0.2388</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.2487448165011203</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2842363249693662</v>
+      </c>
+      <c r="C67">
+        <v>-28.66956527421232</v>
+      </c>
+      <c r="D67">
+        <v>100.9829347257877</v>
+      </c>
+      <c r="E67">
+        <v>141.6025</v>
+      </c>
+      <c r="F67">
+        <v>148.7525</v>
+      </c>
+      <c r="G67">
+        <v>19.1</v>
+      </c>
+      <c r="H67">
+        <v>221.7</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>24.2</v>
+      </c>
+      <c r="K67">
+        <v>15.5</v>
+      </c>
+      <c r="L67">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M67">
+        <v>35.522097</v>
+      </c>
+      <c r="N67">
+        <v>-26.822097</v>
+      </c>
+      <c r="O67">
+        <v>-0</v>
+      </c>
+      <c r="P67">
+        <v>-26.822097</v>
+      </c>
+      <c r="Q67">
+        <v>-11.322097</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.3686180713410463</v>
+      </c>
+      <c r="T67">
+        <v>2.140563432510383</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0</v>
+      </c>
+      <c r="W67">
+        <v>0.2388</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.2449179731703339</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2862363249693662</v>
+      </c>
+      <c r="C68">
+        <v>-31.7742989839418</v>
+      </c>
+      <c r="D68">
+        <v>100.1667010160582</v>
+      </c>
+      <c r="E68">
+        <v>143.891</v>
+      </c>
+      <c r="F68">
+        <v>151.041</v>
+      </c>
+      <c r="G68">
+        <v>19.1</v>
+      </c>
+      <c r="H68">
+        <v>221.7</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>24.2</v>
+      </c>
+      <c r="K68">
+        <v>15.5</v>
+      </c>
+      <c r="L68">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M68">
+        <v>36.0685908</v>
+      </c>
+      <c r="N68">
+        <v>-27.3685908</v>
+      </c>
+      <c r="O68">
+        <v>-0</v>
+      </c>
+      <c r="P68">
+        <v>-27.3685908</v>
+      </c>
+      <c r="Q68">
+        <v>-11.8685908</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.378318602851077</v>
+      </c>
+      <c r="T68">
+        <v>2.203521180525394</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0</v>
+      </c>
+      <c r="W68">
+        <v>0.2388</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.2412070947889652</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2882363249693662</v>
+      </c>
+      <c r="C69">
+        <v>-34.8659434419782</v>
+      </c>
+      <c r="D69">
+        <v>99.36355655802178</v>
+      </c>
+      <c r="E69">
+        <v>146.1795</v>
+      </c>
+      <c r="F69">
+        <v>153.3295</v>
+      </c>
+      <c r="G69">
+        <v>19.1</v>
+      </c>
+      <c r="H69">
+        <v>221.7</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>24.2</v>
+      </c>
+      <c r="K69">
+        <v>15.5</v>
+      </c>
+      <c r="L69">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M69">
+        <v>36.6150846</v>
+      </c>
+      <c r="N69">
+        <v>-27.9150846</v>
+      </c>
+      <c r="O69">
+        <v>-0</v>
+      </c>
+      <c r="P69">
+        <v>-27.9150846</v>
+      </c>
+      <c r="Q69">
+        <v>-12.4150846</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.3886070453617158</v>
+      </c>
+      <c r="T69">
+        <v>2.270294549632224</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0</v>
+      </c>
+      <c r="W69">
+        <v>0.2388</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.2376069888965926</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2902363249693662</v>
+      </c>
+      <c r="C70">
+        <v>-37.94481099583206</v>
+      </c>
+      <c r="D70">
+        <v>98.57318900416793</v>
+      </c>
+      <c r="E70">
+        <v>148.468</v>
+      </c>
+      <c r="F70">
+        <v>155.618</v>
+      </c>
+      <c r="G70">
+        <v>19.1</v>
+      </c>
+      <c r="H70">
+        <v>221.7</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>24.2</v>
+      </c>
+      <c r="K70">
+        <v>15.5</v>
+      </c>
+      <c r="L70">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M70">
+        <v>37.1615784</v>
+      </c>
+      <c r="N70">
+        <v>-28.4615784</v>
+      </c>
+      <c r="O70">
+        <v>-0</v>
+      </c>
+      <c r="P70">
+        <v>-28.4615784</v>
+      </c>
+      <c r="Q70">
+        <v>-12.9615784</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.3995385155292693</v>
+      </c>
+      <c r="T70">
+        <v>2.341241254308231</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0</v>
+      </c>
+      <c r="W70">
+        <v>0.2388</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.2341127684716428</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2922363249693662</v>
+      </c>
+      <c r="C71">
+        <v>-41.01120413341673</v>
+      </c>
+      <c r="D71">
+        <v>97.79529586658329</v>
+      </c>
+      <c r="E71">
+        <v>150.7565</v>
+      </c>
+      <c r="F71">
+        <v>157.9065</v>
+      </c>
+      <c r="G71">
+        <v>19.1</v>
+      </c>
+      <c r="H71">
+        <v>221.7</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>24.2</v>
+      </c>
+      <c r="K71">
+        <v>15.5</v>
+      </c>
+      <c r="L71">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M71">
+        <v>37.70807220000001</v>
+      </c>
+      <c r="N71">
+        <v>-29.00807220000001</v>
+      </c>
+      <c r="O71">
+        <v>-0</v>
+      </c>
+      <c r="P71">
+        <v>-29.00807220000001</v>
+      </c>
+      <c r="Q71">
+        <v>-13.50807220000001</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.4111752418366652</v>
+      </c>
+      <c r="T71">
+        <v>2.416765165737529</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0</v>
+      </c>
+      <c r="W71">
+        <v>0.2388</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.2307198297981405</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2942363249693662</v>
+      </c>
+      <c r="C72">
+        <v>-44.06541586903859</v>
+      </c>
+      <c r="D72">
+        <v>97.02958413096144</v>
+      </c>
+      <c r="E72">
+        <v>153.045</v>
+      </c>
+      <c r="F72">
+        <v>160.195</v>
+      </c>
+      <c r="G72">
+        <v>19.1</v>
+      </c>
+      <c r="H72">
+        <v>221.7</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>24.2</v>
+      </c>
+      <c r="K72">
+        <v>15.5</v>
+      </c>
+      <c r="L72">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M72">
+        <v>38.254566</v>
+      </c>
+      <c r="N72">
+        <v>-29.554566</v>
+      </c>
+      <c r="O72">
+        <v>-0</v>
+      </c>
+      <c r="P72">
+        <v>-29.554566</v>
+      </c>
+      <c r="Q72">
+        <v>-14.054566</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.4235877498978873</v>
+      </c>
+      <c r="T72">
+        <v>2.497324004595447</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0</v>
+      </c>
+      <c r="W72">
+        <v>0.2388</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.2274238322295957</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2962363249693662</v>
+      </c>
+      <c r="C73">
+        <v>-47.10773011139543</v>
+      </c>
+      <c r="D73">
+        <v>96.27576988860457</v>
+      </c>
+      <c r="E73">
+        <v>155.3335</v>
+      </c>
+      <c r="F73">
+        <v>162.4835</v>
+      </c>
+      <c r="G73">
+        <v>19.1</v>
+      </c>
+      <c r="H73">
+        <v>221.7</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>24.2</v>
+      </c>
+      <c r="K73">
+        <v>15.5</v>
+      </c>
+      <c r="L73">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M73">
+        <v>38.8010598</v>
+      </c>
+      <c r="N73">
+        <v>-30.1010598</v>
+      </c>
+      <c r="O73">
+        <v>-0</v>
+      </c>
+      <c r="P73">
+        <v>-30.1010598</v>
+      </c>
+      <c r="Q73">
+        <v>-14.6010598</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.4368562929978144</v>
+      </c>
+      <c r="T73">
+        <v>2.583438625443565</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0</v>
+      </c>
+      <c r="W73">
+        <v>0.2388</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.2242206796629818</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2982363249693662</v>
+      </c>
+      <c r="C74">
+        <v>-50.13842201455296</v>
+      </c>
+      <c r="D74">
+        <v>95.53357798544702</v>
+      </c>
+      <c r="E74">
+        <v>157.622</v>
+      </c>
+      <c r="F74">
+        <v>164.772</v>
+      </c>
+      <c r="G74">
+        <v>19.1</v>
+      </c>
+      <c r="H74">
+        <v>221.7</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>24.2</v>
+      </c>
+      <c r="K74">
+        <v>15.5</v>
+      </c>
+      <c r="L74">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M74">
+        <v>39.3475536</v>
+      </c>
+      <c r="N74">
+        <v>-30.6475536</v>
+      </c>
+      <c r="O74">
+        <v>-0</v>
+      </c>
+      <c r="P74">
+        <v>-30.6475536</v>
+      </c>
+      <c r="Q74">
+        <v>-15.1475536</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.4510725891763078</v>
+      </c>
+      <c r="T74">
+        <v>2.675704290637978</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0</v>
+      </c>
+      <c r="W74">
+        <v>0.2388</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.2211065035565515</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.3002363249693661</v>
+      </c>
+      <c r="C75">
+        <v>-53.15775831281132</v>
+      </c>
+      <c r="D75">
+        <v>94.80274168718866</v>
+      </c>
+      <c r="E75">
+        <v>159.9105</v>
+      </c>
+      <c r="F75">
+        <v>167.0605</v>
+      </c>
+      <c r="G75">
+        <v>19.1</v>
+      </c>
+      <c r="H75">
+        <v>221.7</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>24.2</v>
+      </c>
+      <c r="K75">
+        <v>15.5</v>
+      </c>
+      <c r="L75">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M75">
+        <v>39.8940474</v>
+      </c>
+      <c r="N75">
+        <v>-31.1940474</v>
+      </c>
+      <c r="O75">
+        <v>-0</v>
+      </c>
+      <c r="P75">
+        <v>-31.1940474</v>
+      </c>
+      <c r="Q75">
+        <v>-15.6940474</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.4663419443309858</v>
+      </c>
+      <c r="T75">
+        <v>2.774804449550496</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0</v>
+      </c>
+      <c r="W75">
+        <v>0.2388</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.218077647343448</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.3022363249693662</v>
+      </c>
+      <c r="C76">
+        <v>-56.16599764031841</v>
+      </c>
+      <c r="D76">
+        <v>94.08300235968159</v>
+      </c>
+      <c r="E76">
+        <v>162.199</v>
+      </c>
+      <c r="F76">
+        <v>169.349</v>
+      </c>
+      <c r="G76">
+        <v>19.1</v>
+      </c>
+      <c r="H76">
+        <v>221.7</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>24.2</v>
+      </c>
+      <c r="K76">
+        <v>15.5</v>
+      </c>
+      <c r="L76">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M76">
+        <v>40.4405412</v>
+      </c>
+      <c r="N76">
+        <v>-31.7405412</v>
+      </c>
+      <c r="O76">
+        <v>-0</v>
+      </c>
+      <c r="P76">
+        <v>-31.7405412</v>
+      </c>
+      <c r="Q76">
+        <v>-16.2405412</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.482785865266793</v>
+      </c>
+      <c r="T76">
+        <v>2.88152769761013</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0</v>
+      </c>
+      <c r="W76">
+        <v>0.2388</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.2151306521090771</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.3042363249693661</v>
+      </c>
+      <c r="C77">
+        <v>-59.16339083623299</v>
+      </c>
+      <c r="D77">
+        <v>93.37410916376699</v>
+      </c>
+      <c r="E77">
+        <v>164.4875</v>
+      </c>
+      <c r="F77">
+        <v>171.6375</v>
+      </c>
+      <c r="G77">
+        <v>19.1</v>
+      </c>
+      <c r="H77">
+        <v>221.7</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>24.2</v>
+      </c>
+      <c r="K77">
+        <v>15.5</v>
+      </c>
+      <c r="L77">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M77">
+        <v>40.987035</v>
+      </c>
+      <c r="N77">
+        <v>-32.287035</v>
+      </c>
+      <c r="O77">
+        <v>-0</v>
+      </c>
+      <c r="P77">
+        <v>-32.287035</v>
+      </c>
+      <c r="Q77">
+        <v>-16.787035</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.5005452998774647</v>
+      </c>
+      <c r="T77">
+        <v>2.996788805514536</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0</v>
+      </c>
+      <c r="W77">
+        <v>0.2388</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.2122622434142893</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.3062363249693662</v>
+      </c>
+      <c r="C78">
+        <v>-62.15018123619618</v>
+      </c>
+      <c r="D78">
+        <v>92.67581876380382</v>
+      </c>
+      <c r="E78">
+        <v>166.776</v>
+      </c>
+      <c r="F78">
+        <v>173.926</v>
+      </c>
+      <c r="G78">
+        <v>19.1</v>
+      </c>
+      <c r="H78">
+        <v>221.7</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>24.2</v>
+      </c>
+      <c r="K78">
+        <v>15.5</v>
+      </c>
+      <c r="L78">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M78">
+        <v>41.5335288</v>
+      </c>
+      <c r="N78">
+        <v>-32.8335288</v>
+      </c>
+      <c r="O78">
+        <v>-0</v>
+      </c>
+      <c r="P78">
+        <v>-32.8335288</v>
+      </c>
+      <c r="Q78">
+        <v>-17.3335288</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.5197846873723592</v>
+      </c>
+      <c r="T78">
+        <v>3.121655005744308</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0</v>
+      </c>
+      <c r="W78">
+        <v>0.2388</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.2094693191588383</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.3082363249693661</v>
+      </c>
+      <c r="C79">
+        <v>-65.12660495082031</v>
+      </c>
+      <c r="D79">
+        <v>91.98789504917968</v>
+      </c>
+      <c r="E79">
+        <v>169.0645</v>
+      </c>
+      <c r="F79">
+        <v>176.2145</v>
+      </c>
+      <c r="G79">
+        <v>19.1</v>
+      </c>
+      <c r="H79">
+        <v>221.7</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>24.2</v>
+      </c>
+      <c r="K79">
+        <v>15.5</v>
+      </c>
+      <c r="L79">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M79">
+        <v>42.0800226</v>
+      </c>
+      <c r="N79">
+        <v>-33.3800226</v>
+      </c>
+      <c r="O79">
+        <v>-0</v>
+      </c>
+      <c r="P79">
+        <v>-33.3800226</v>
+      </c>
+      <c r="Q79">
+        <v>-17.8800226</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.5406970650842007</v>
+      </c>
+      <c r="T79">
+        <v>3.257379136428843</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0</v>
+      </c>
+      <c r="W79">
+        <v>0.2388</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.2067489383905415</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.3102363249693662</v>
+      </c>
+      <c r="C80">
+        <v>-68.09289113186713</v>
+      </c>
+      <c r="D80">
+        <v>91.31010886813289</v>
+      </c>
+      <c r="E80">
+        <v>171.353</v>
+      </c>
+      <c r="F80">
+        <v>178.503</v>
+      </c>
+      <c r="G80">
+        <v>19.1</v>
+      </c>
+      <c r="H80">
+        <v>221.7</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>24.2</v>
+      </c>
+      <c r="K80">
+        <v>15.5</v>
+      </c>
+      <c r="L80">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M80">
+        <v>42.62651640000001</v>
+      </c>
+      <c r="N80">
+        <v>-33.92651640000001</v>
+      </c>
+      <c r="O80">
+        <v>-0</v>
+      </c>
+      <c r="P80">
+        <v>-33.92651640000001</v>
+      </c>
+      <c r="Q80">
+        <v>-18.42651640000001</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.5635105680425736</v>
+      </c>
+      <c r="T80">
+        <v>3.405441824448336</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0</v>
+      </c>
+      <c r="W80">
+        <v>0.2388</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.2040983109752782</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.3122363249693662</v>
+      </c>
+      <c r="C81">
+        <v>-71.04926222674351</v>
+      </c>
+      <c r="D81">
+        <v>90.6422377732565</v>
+      </c>
+      <c r="E81">
+        <v>173.6415</v>
+      </c>
+      <c r="F81">
+        <v>180.7915</v>
+      </c>
+      <c r="G81">
+        <v>19.1</v>
+      </c>
+      <c r="H81">
+        <v>221.7</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>24.2</v>
+      </c>
+      <c r="K81">
+        <v>15.5</v>
+      </c>
+      <c r="L81">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M81">
+        <v>43.17301020000001</v>
+      </c>
+      <c r="N81">
+        <v>-34.4730102</v>
+      </c>
+      <c r="O81">
+        <v>-0</v>
+      </c>
+      <c r="P81">
+        <v>-34.4730102</v>
+      </c>
+      <c r="Q81">
+        <v>-18.9730102</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.5884967855684105</v>
+      </c>
+      <c r="T81">
+        <v>3.567605720850638</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0</v>
+      </c>
+      <c r="W81">
+        <v>0.2388</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.2015147880515407</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.3142363249693662</v>
+      </c>
+      <c r="C82">
+        <v>-73.99593422191037</v>
+      </c>
+      <c r="D82">
+        <v>89.98406577808963</v>
+      </c>
+      <c r="E82">
+        <v>175.93</v>
+      </c>
+      <c r="F82">
+        <v>183.08</v>
+      </c>
+      <c r="G82">
+        <v>19.1</v>
+      </c>
+      <c r="H82">
+        <v>221.7</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>24.2</v>
+      </c>
+      <c r="K82">
+        <v>15.5</v>
+      </c>
+      <c r="L82">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M82">
+        <v>43.71950400000001</v>
+      </c>
+      <c r="N82">
+        <v>-35.01950400000001</v>
+      </c>
+      <c r="O82">
+        <v>-0</v>
+      </c>
+      <c r="P82">
+        <v>-35.01950400000001</v>
+      </c>
+      <c r="Q82">
+        <v>-19.51950400000001</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.6159816248468311</v>
+      </c>
+      <c r="T82">
+        <v>3.74598600689317</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0</v>
+      </c>
+      <c r="W82">
+        <v>0.2388</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.1989958532008962</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.3162363249693662</v>
+      </c>
+      <c r="C83">
+        <v>-76.93311687576272</v>
+      </c>
+      <c r="D83">
+        <v>89.3353831242373</v>
+      </c>
+      <c r="E83">
+        <v>178.2185</v>
+      </c>
+      <c r="F83">
+        <v>185.3685</v>
+      </c>
+      <c r="G83">
+        <v>19.1</v>
+      </c>
+      <c r="H83">
+        <v>221.7</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>24.2</v>
+      </c>
+      <c r="K83">
+        <v>15.5</v>
+      </c>
+      <c r="L83">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M83">
+        <v>44.26599780000001</v>
+      </c>
+      <c r="N83">
+        <v>-35.56599780000001</v>
+      </c>
+      <c r="O83">
+        <v>-0</v>
+      </c>
+      <c r="P83">
+        <v>-35.56599780000001</v>
+      </c>
+      <c r="Q83">
+        <v>-20.06599780000001</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.6463596051019274</v>
+      </c>
+      <c r="T83">
+        <v>3.943143165150706</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0</v>
+      </c>
+      <c r="W83">
+        <v>0.2388</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.1965391142724903</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.3182363249693662</v>
+      </c>
+      <c r="C84">
+        <v>-79.8610139415095</v>
+      </c>
+      <c r="D84">
+        <v>88.6959860584905</v>
+      </c>
+      <c r="E84">
+        <v>180.507</v>
+      </c>
+      <c r="F84">
+        <v>187.657</v>
+      </c>
+      <c r="G84">
+        <v>19.1</v>
+      </c>
+      <c r="H84">
+        <v>221.7</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>24.2</v>
+      </c>
+      <c r="K84">
+        <v>15.5</v>
+      </c>
+      <c r="L84">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M84">
+        <v>44.8124916</v>
+      </c>
+      <c r="N84">
+        <v>-36.1124916</v>
+      </c>
+      <c r="O84">
+        <v>-0</v>
+      </c>
+      <c r="P84">
+        <v>-36.1124916</v>
+      </c>
+      <c r="Q84">
+        <v>-20.6124916</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.680112916496479</v>
+      </c>
+      <c r="T84">
+        <v>4.162206674325745</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0</v>
+      </c>
+      <c r="W84">
+        <v>0.2388</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.1941422958057526</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.3202363249693662</v>
+      </c>
+      <c r="C85">
+        <v>-82.77982338054971</v>
+      </c>
+      <c r="D85">
+        <v>88.06567661945029</v>
+      </c>
+      <c r="E85">
+        <v>182.7955</v>
+      </c>
+      <c r="F85">
+        <v>189.9455</v>
+      </c>
+      <c r="G85">
+        <v>19.1</v>
+      </c>
+      <c r="H85">
+        <v>221.7</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>24.2</v>
+      </c>
+      <c r="K85">
+        <v>15.5</v>
+      </c>
+      <c r="L85">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M85">
+        <v>45.3589854</v>
+      </c>
+      <c r="N85">
+        <v>-36.65898540000001</v>
+      </c>
+      <c r="O85">
+        <v>-0</v>
+      </c>
+      <c r="P85">
+        <v>-36.65898540000001</v>
+      </c>
+      <c r="Q85">
+        <v>-21.15898540000001</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.7178372057021543</v>
+      </c>
+      <c r="T85">
+        <v>4.407042361050789</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0</v>
+      </c>
+      <c r="W85">
+        <v>0.2388</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.1918032320008638</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.3222363249693662</v>
+      </c>
+      <c r="C86">
+        <v>-85.6897375668151</v>
+      </c>
+      <c r="D86">
+        <v>87.44426243318487</v>
+      </c>
+      <c r="E86">
+        <v>185.084</v>
+      </c>
+      <c r="F86">
+        <v>192.234</v>
+      </c>
+      <c r="G86">
+        <v>19.1</v>
+      </c>
+      <c r="H86">
+        <v>221.7</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>24.2</v>
+      </c>
+      <c r="K86">
+        <v>15.5</v>
+      </c>
+      <c r="L86">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M86">
+        <v>45.90547919999999</v>
+      </c>
+      <c r="N86">
+        <v>-37.2054792</v>
+      </c>
+      <c r="O86">
+        <v>-0</v>
+      </c>
+      <c r="P86">
+        <v>-37.2054792</v>
+      </c>
+      <c r="Q86">
+        <v>-21.7054792</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.7602770310585385</v>
+      </c>
+      <c r="T86">
+        <v>4.682482508616461</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0</v>
+      </c>
+      <c r="W86">
+        <v>0.2388</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.1895198601913297</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.3242363249693662</v>
+      </c>
+      <c r="C87">
+        <v>-88.59094348252205</v>
+      </c>
+      <c r="D87">
+        <v>86.83155651747794</v>
+      </c>
+      <c r="E87">
+        <v>187.3725</v>
+      </c>
+      <c r="F87">
+        <v>194.5225</v>
+      </c>
+      <c r="G87">
+        <v>19.1</v>
+      </c>
+      <c r="H87">
+        <v>221.7</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>24.2</v>
+      </c>
+      <c r="K87">
+        <v>15.5</v>
+      </c>
+      <c r="L87">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M87">
+        <v>46.451973</v>
+      </c>
+      <c r="N87">
+        <v>-37.75197299999999</v>
+      </c>
+      <c r="O87">
+        <v>-0</v>
+      </c>
+      <c r="P87">
+        <v>-37.75197299999999</v>
+      </c>
+      <c r="Q87">
+        <v>-22.25197299999999</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.8083754997957746</v>
+      </c>
+      <c r="T87">
+        <v>4.994648009190892</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0</v>
+      </c>
+      <c r="W87">
+        <v>0.2388</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.1872902147773142</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.3262363249693662</v>
+      </c>
+      <c r="C88">
+        <v>-91.48362290575068</v>
+      </c>
+      <c r="D88">
+        <v>86.22737709424931</v>
+      </c>
+      <c r="E88">
+        <v>189.661</v>
+      </c>
+      <c r="F88">
+        <v>196.811</v>
+      </c>
+      <c r="G88">
+        <v>19.1</v>
+      </c>
+      <c r="H88">
+        <v>221.7</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>24.2</v>
+      </c>
+      <c r="K88">
+        <v>15.5</v>
+      </c>
+      <c r="L88">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M88">
+        <v>46.9984668</v>
+      </c>
+      <c r="N88">
+        <v>-38.2984668</v>
+      </c>
+      <c r="O88">
+        <v>-0</v>
+      </c>
+      <c r="P88">
+        <v>-38.2984668</v>
+      </c>
+      <c r="Q88">
+        <v>-22.7984668</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.8633451783526156</v>
+      </c>
+      <c r="T88">
+        <v>5.351408581275956</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0</v>
+      </c>
+      <c r="W88">
+        <v>0.2388</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.1851124215822291</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.3282363249693662</v>
+      </c>
+      <c r="C89">
+        <v>-94.36795259024782</v>
+      </c>
+      <c r="D89">
+        <v>85.63154740975219</v>
+      </c>
+      <c r="E89">
+        <v>191.9495</v>
+      </c>
+      <c r="F89">
+        <v>199.0995</v>
+      </c>
+      <c r="G89">
+        <v>19.1</v>
+      </c>
+      <c r="H89">
+        <v>221.7</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>24.2</v>
+      </c>
+      <c r="K89">
+        <v>15.5</v>
+      </c>
+      <c r="L89">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M89">
+        <v>47.5449606</v>
+      </c>
+      <c r="N89">
+        <v>-38.84496060000001</v>
+      </c>
+      <c r="O89">
+        <v>-0</v>
+      </c>
+      <c r="P89">
+        <v>-38.84496060000001</v>
+      </c>
+      <c r="Q89">
+        <v>-23.34496060000001</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.9267717305335861</v>
+      </c>
+      <c r="T89">
+        <v>5.763055395220261</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0</v>
+      </c>
+      <c r="W89">
+        <v>0.2388</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.1829846925985252</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.3302363249693662</v>
+      </c>
+      <c r="C90">
+        <v>-97.24410443782554</v>
+      </c>
+      <c r="D90">
+        <v>85.04389556217447</v>
+      </c>
+      <c r="E90">
+        <v>194.238</v>
+      </c>
+      <c r="F90">
+        <v>201.388</v>
+      </c>
+      <c r="G90">
+        <v>19.1</v>
+      </c>
+      <c r="H90">
+        <v>221.7</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>24.2</v>
+      </c>
+      <c r="K90">
+        <v>15.5</v>
+      </c>
+      <c r="L90">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M90">
+        <v>48.0914544</v>
+      </c>
+      <c r="N90">
+        <v>-39.3914544</v>
+      </c>
+      <c r="O90">
+        <v>-0</v>
+      </c>
+      <c r="P90">
+        <v>-39.3914544</v>
+      </c>
+      <c r="Q90">
+        <v>-23.8914544</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>1.000769374744718</v>
+      </c>
+      <c r="T90">
+        <v>6.243310011488616</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0</v>
+      </c>
+      <c r="W90">
+        <v>0.2388</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.180905321091724</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.3322363249693662</v>
+      </c>
+      <c r="C91">
+        <v>-100.1122456637102</v>
+      </c>
+      <c r="D91">
+        <v>84.46425433628978</v>
+      </c>
+      <c r="E91">
+        <v>196.5265</v>
+      </c>
+      <c r="F91">
+        <v>203.6765</v>
+      </c>
+      <c r="G91">
+        <v>19.1</v>
+      </c>
+      <c r="H91">
+        <v>221.7</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>24.2</v>
+      </c>
+      <c r="K91">
+        <v>15.5</v>
+      </c>
+      <c r="L91">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M91">
+        <v>48.6379482</v>
+      </c>
+      <c r="N91">
+        <v>-39.93794820000001</v>
+      </c>
+      <c r="O91">
+        <v>-0</v>
+      </c>
+      <c r="P91">
+        <v>-39.93794820000001</v>
+      </c>
+      <c r="Q91">
+        <v>-24.43794820000001</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>1.088221136085147</v>
+      </c>
+      <c r="T91">
+        <v>6.810883648896672</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0</v>
+      </c>
+      <c r="W91">
+        <v>0.2388</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.1788726770345135</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.3342363249693662</v>
+      </c>
+      <c r="C92">
+        <v>-102.9725389551753</v>
+      </c>
+      <c r="D92">
+        <v>83.8924610448247</v>
+      </c>
+      <c r="E92">
+        <v>198.815</v>
+      </c>
+      <c r="F92">
+        <v>205.965</v>
+      </c>
+      <c r="G92">
+        <v>19.1</v>
+      </c>
+      <c r="H92">
+        <v>221.7</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>24.2</v>
+      </c>
+      <c r="K92">
+        <v>15.5</v>
+      </c>
+      <c r="L92">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M92">
+        <v>49.184442</v>
+      </c>
+      <c r="N92">
+        <v>-40.484442</v>
+      </c>
+      <c r="O92">
+        <v>-0</v>
+      </c>
+      <c r="P92">
+        <v>-40.484442</v>
+      </c>
+      <c r="Q92">
+        <v>-24.984442</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>1.193163249693662</v>
+      </c>
+      <c r="T92">
+        <v>7.49197201378634</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0</v>
+      </c>
+      <c r="W92">
+        <v>0.2388</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.1768852028452412</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.3362363249693662</v>
+      </c>
+      <c r="C93">
+        <v>-105.8251426237737</v>
+      </c>
+      <c r="D93">
+        <v>83.32835737622628</v>
+      </c>
+      <c r="E93">
+        <v>201.1035</v>
+      </c>
+      <c r="F93">
+        <v>208.2535</v>
+      </c>
+      <c r="G93">
+        <v>19.1</v>
+      </c>
+      <c r="H93">
+        <v>221.7</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>24.2</v>
+      </c>
+      <c r="K93">
+        <v>15.5</v>
+      </c>
+      <c r="L93">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M93">
+        <v>49.7309358</v>
+      </c>
+      <c r="N93">
+        <v>-41.03093580000001</v>
+      </c>
+      <c r="O93">
+        <v>-0</v>
+      </c>
+      <c r="P93">
+        <v>-41.03093580000001</v>
+      </c>
+      <c r="Q93">
+        <v>-25.53093580000001</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>1.321425832992958</v>
+      </c>
+      <c r="T93">
+        <v>8.32441334865149</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0</v>
+      </c>
+      <c r="W93">
+        <v>0.2388</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.1749414094073813</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.3382363249693662</v>
+      </c>
+      <c r="C94">
+        <v>-108.67021075147</v>
+      </c>
+      <c r="D94">
+        <v>82.77178924853001</v>
+      </c>
+      <c r="E94">
+        <v>203.392</v>
+      </c>
+      <c r="F94">
+        <v>210.542</v>
+      </c>
+      <c r="G94">
+        <v>19.1</v>
+      </c>
+      <c r="H94">
+        <v>221.7</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>24.2</v>
+      </c>
+      <c r="K94">
+        <v>15.5</v>
+      </c>
+      <c r="L94">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M94">
+        <v>50.2774296</v>
+      </c>
+      <c r="N94">
+        <v>-41.5774296</v>
+      </c>
+      <c r="O94">
+        <v>-0</v>
+      </c>
+      <c r="P94">
+        <v>-41.5774296</v>
+      </c>
+      <c r="Q94">
+        <v>-26.0774296</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>1.481754062117078</v>
+      </c>
+      <c r="T94">
+        <v>9.36496501723293</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0</v>
+      </c>
+      <c r="W94">
+        <v>0.2388</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.1730398723486055</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.3402363249693662</v>
+      </c>
+      <c r="C95">
+        <v>-111.5078933309547</v>
+      </c>
+      <c r="D95">
+        <v>82.22260666904532</v>
+      </c>
+      <c r="E95">
+        <v>205.6805</v>
+      </c>
+      <c r="F95">
+        <v>212.8305</v>
+      </c>
+      <c r="G95">
+        <v>19.1</v>
+      </c>
+      <c r="H95">
+        <v>221.7</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>24.2</v>
+      </c>
+      <c r="K95">
+        <v>15.5</v>
+      </c>
+      <c r="L95">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M95">
+        <v>50.82392340000001</v>
+      </c>
+      <c r="N95">
+        <v>-42.12392340000001</v>
+      </c>
+      <c r="O95">
+        <v>-0</v>
+      </c>
+      <c r="P95">
+        <v>-42.12392340000001</v>
+      </c>
+      <c r="Q95">
+        <v>-26.62392340000001</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.687890356705232</v>
+      </c>
+      <c r="T95">
+        <v>10.70281716255192</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0</v>
+      </c>
+      <c r="W95">
+        <v>0.2388</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.1711792285599107</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.3422363249693662</v>
+      </c>
+      <c r="C96">
+        <v>-114.3383364004098</v>
+      </c>
+      <c r="D96">
+        <v>81.68066359959018</v>
+      </c>
+      <c r="E96">
+        <v>207.969</v>
+      </c>
+      <c r="F96">
+        <v>215.119</v>
+      </c>
+      <c r="G96">
+        <v>19.1</v>
+      </c>
+      <c r="H96">
+        <v>221.7</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>24.2</v>
+      </c>
+      <c r="K96">
+        <v>15.5</v>
+      </c>
+      <c r="L96">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M96">
+        <v>51.37041720000001</v>
+      </c>
+      <c r="N96">
+        <v>-42.6704172</v>
+      </c>
+      <c r="O96">
+        <v>-0</v>
+      </c>
+      <c r="P96">
+        <v>-42.6704172</v>
+      </c>
+      <c r="Q96">
+        <v>-27.1704172</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.962738749489438</v>
+      </c>
+      <c r="T96">
+        <v>12.48662002297724</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0</v>
+      </c>
+      <c r="W96">
+        <v>0.2388</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.1693581729369331</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.3442363249693662</v>
+      </c>
+      <c r="C97">
+        <v>-117.1616821729798</v>
+      </c>
+      <c r="D97">
+        <v>81.14581782702018</v>
+      </c>
+      <c r="E97">
+        <v>210.2575</v>
+      </c>
+      <c r="F97">
+        <v>217.4075</v>
+      </c>
+      <c r="G97">
+        <v>19.1</v>
+      </c>
+      <c r="H97">
+        <v>221.7</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>24.2</v>
+      </c>
+      <c r="K97">
+        <v>15.5</v>
+      </c>
+      <c r="L97">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M97">
+        <v>51.916911</v>
+      </c>
+      <c r="N97">
+        <v>-43.216911</v>
+      </c>
+      <c r="O97">
+        <v>-0</v>
+      </c>
+      <c r="P97">
+        <v>-43.216911</v>
+      </c>
+      <c r="Q97">
+        <v>-27.716911</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>2.347526499387327</v>
+      </c>
+      <c r="T97">
+        <v>14.9839440275727</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0</v>
+      </c>
+      <c r="W97">
+        <v>0.2388</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.1675754553270706</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.3462363249693662</v>
+      </c>
+      <c r="C98">
+        <v>-119.9780691611886</v>
+      </c>
+      <c r="D98">
+        <v>80.61793083881145</v>
+      </c>
+      <c r="E98">
+        <v>212.546</v>
+      </c>
+      <c r="F98">
+        <v>219.696</v>
+      </c>
+      <c r="G98">
+        <v>19.1</v>
+      </c>
+      <c r="H98">
+        <v>221.7</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>24.2</v>
+      </c>
+      <c r="K98">
+        <v>15.5</v>
+      </c>
+      <c r="L98">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M98">
+        <v>52.4634048</v>
+      </c>
+      <c r="N98">
+        <v>-43.7634048</v>
+      </c>
+      <c r="O98">
+        <v>-0</v>
+      </c>
+      <c r="P98">
+        <v>-43.7634048</v>
+      </c>
+      <c r="Q98">
+        <v>-28.2634048</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>2.924708124234152</v>
+      </c>
+      <c r="T98">
+        <v>18.72993003446583</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0</v>
+      </c>
+      <c r="W98">
+        <v>0.2388</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.1658298776674135</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.3482363249693662</v>
+      </c>
+      <c r="C99">
+        <v>-122.7876322965318</v>
+      </c>
+      <c r="D99">
+        <v>80.09686770346822</v>
+      </c>
+      <c r="E99">
+        <v>214.8345</v>
+      </c>
+      <c r="F99">
+        <v>221.9845</v>
+      </c>
+      <c r="G99">
+        <v>19.1</v>
+      </c>
+      <c r="H99">
+        <v>221.7</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>24.2</v>
+      </c>
+      <c r="K99">
+        <v>15.5</v>
+      </c>
+      <c r="L99">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M99">
+        <v>53.0098986</v>
+      </c>
+      <c r="N99">
+        <v>-44.3098986</v>
+      </c>
+      <c r="O99">
+        <v>-0</v>
+      </c>
+      <c r="P99">
+        <v>-44.3098986</v>
+      </c>
+      <c r="Q99">
+        <v>-28.8098986</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>3.88667749897887</v>
+      </c>
+      <c r="T99">
+        <v>24.97324004595444</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0</v>
+      </c>
+      <c r="W99">
+        <v>0.2388</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.1641202912997084</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.3502363249693662</v>
+      </c>
+      <c r="C100">
+        <v>-125.5905030444614</v>
+      </c>
+      <c r="D100">
+        <v>79.58249695553863</v>
+      </c>
+      <c r="E100">
+        <v>217.123</v>
+      </c>
+      <c r="F100">
+        <v>224.273</v>
+      </c>
+      <c r="G100">
+        <v>19.1</v>
+      </c>
+      <c r="H100">
+        <v>221.7</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>24.2</v>
+      </c>
+      <c r="K100">
+        <v>15.5</v>
+      </c>
+      <c r="L100">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M100">
+        <v>53.5563924</v>
+      </c>
+      <c r="N100">
+        <v>-44.8563924</v>
+      </c>
+      <c r="O100">
+        <v>-0</v>
+      </c>
+      <c r="P100">
+        <v>-44.8563924</v>
+      </c>
+      <c r="Q100">
+        <v>-29.3563924</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>5.810616248468304</v>
+      </c>
+      <c r="T100">
+        <v>37.45986006893166</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0</v>
+      </c>
+      <c r="W100">
+        <v>0.2388</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.1624455944497112</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.3522363249693662</v>
+      </c>
+      <c r="C101">
+        <v>-128.3868095149674</v>
+      </c>
+      <c r="D101">
+        <v>79.07469048503259</v>
+      </c>
+      <c r="E101">
+        <v>219.4115</v>
+      </c>
+      <c r="F101">
+        <v>226.5615</v>
+      </c>
+      <c r="G101">
+        <v>19.1</v>
+      </c>
+      <c r="H101">
+        <v>221.7</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>24.2</v>
+      </c>
+      <c r="K101">
+        <v>15.5</v>
+      </c>
+      <c r="L101">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M101">
+        <v>54.1028862</v>
+      </c>
+      <c r="N101">
+        <v>-45.4028862</v>
+      </c>
+      <c r="O101">
+        <v>-0</v>
+      </c>
+      <c r="P101">
+        <v>-45.4028862</v>
+      </c>
+      <c r="Q101">
+        <v>-29.9028862</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>11.58243249693661</v>
+      </c>
+      <c r="T101">
+        <v>74.91972013786332</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0</v>
+      </c>
+      <c r="W101">
+        <v>0.2388</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.1608047298593103</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
